--- a/daily/2026-04-03.xlsx
+++ b/daily/2026-04-03.xlsx
@@ -722,7 +722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -736,75 +736,75 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9</v>
+        <v>20.6</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4</v>
+        <v>20.7</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>20.1</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>27.9</v>
       </c>
       <c r="K4" t="n">
-        <v>19.7</v>
+        <v>28.2</v>
       </c>
       <c r="L4" t="n">
-        <v>58.5</v>
+        <v>43.4</v>
       </c>
       <c r="M4" t="n">
-        <v>53.9</v>
+        <v>40.6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>7.6 (5g)</t>
+          <t>25.5 (4g)</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -818,75 +818,75 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7</v>
+        <v>6.7</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6</v>
+        <v>7.6</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>7.9</v>
       </c>
       <c r="H5" t="n">
-        <v>18.1</v>
+        <v>8.4</v>
       </c>
       <c r="I5" t="n">
-        <v>18.9</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>28.5</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>30.9</v>
+        <v>19.7</v>
       </c>
       <c r="L5" t="n">
-        <v>42.8</v>
+        <v>58.5</v>
       </c>
       <c r="M5" t="n">
-        <v>47.4</v>
+        <v>53.9</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="R5" t="n">
-        <v>-3.3</v>
+        <v>-0.2</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.6</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.3</v>
+        <v>-0.7</v>
       </c>
       <c r="U5" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>24.7 (3g)</t>
+          <t>7.6 (5g)</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -896,79 +896,79 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
       <c r="E6" t="n">
-        <v>12.7</v>
+        <v>13.7</v>
       </c>
       <c r="F6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5</v>
+        <v>18.1</v>
       </c>
       <c r="I6" t="n">
-        <v>10.8</v>
+        <v>18.9</v>
       </c>
       <c r="J6" t="n">
-        <v>16.9</v>
+        <v>28.5</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>30.9</v>
       </c>
       <c r="L6" t="n">
-        <v>57.8</v>
+        <v>42.8</v>
       </c>
       <c r="M6" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P6" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>-3.3</v>
       </c>
       <c r="S6" t="n">
-        <v>9.699999999999999</v>
+        <v>-4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1</v>
+        <v>-2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="V6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>6.0 (4g)</t>
+          <t>24.7 (3g)</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>-19.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -982,75 +982,75 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E7" t="n">
-        <v>18.3</v>
+        <v>12.7</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>12.2</v>
       </c>
       <c r="G7" t="n">
-        <v>18.7</v>
+        <v>12.4</v>
       </c>
       <c r="H7" t="n">
-        <v>20.1</v>
+        <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>20.3</v>
+        <v>10.8</v>
       </c>
       <c r="J7" t="n">
-        <v>30.3</v>
+        <v>16.9</v>
       </c>
       <c r="K7" t="n">
-        <v>30.4</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
-        <v>45.9</v>
+        <v>57.8</v>
       </c>
       <c r="M7" t="n">
-        <v>45.3</v>
+        <v>48.1</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P7" t="n">
         <v>57</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>23.5 (4g)</t>
+          <t>6.0 (4g)</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11.4</v>
+        <v>-19.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1064,55 +1064,55 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="E8" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="F8" t="n">
-        <v>17.2</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="H8" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
       <c r="I8" t="n">
-        <v>14.6</v>
+        <v>20.3</v>
       </c>
       <c r="J8" t="n">
-        <v>28</v>
+        <v>30.3</v>
       </c>
       <c r="K8" t="n">
-        <v>28.6</v>
+        <v>30.4</v>
       </c>
       <c r="L8" t="n">
-        <v>54.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="n">
-        <v>47.1</v>
+        <v>45.3</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P8" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="S8" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="U8" t="n">
         <v>20</v>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>17.2 (4g)</t>
+          <t>23.5 (4g)</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1146,34 +1146,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="E9" t="n">
-        <v>15.3</v>
+        <v>19.3</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>17.2</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>9.4</v>
+        <v>14.2</v>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>14.6</v>
       </c>
       <c r="J9" t="n">
-        <v>23.4</v>
+        <v>28</v>
       </c>
       <c r="K9" t="n">
-        <v>19.1</v>
+        <v>28.6</v>
       </c>
       <c r="L9" t="n">
-        <v>55.3</v>
+        <v>54.3</v>
       </c>
       <c r="M9" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
       <c r="N9" t="n">
         <v>5.2</v>
@@ -1182,39 +1182,39 @@
         <v>40</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3</v>
+        <v>0.1</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T9" t="n">
-        <v>4.3</v>
+        <v>-0.6</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.0 (5g)</t>
+          <t>17.2 (4g)</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>-6.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1228,75 +1228,75 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>15.3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J10" t="n">
-        <v>26.5</v>
+        <v>23.4</v>
       </c>
       <c r="K10" t="n">
-        <v>27.9</v>
+        <v>19.1</v>
       </c>
       <c r="L10" t="n">
-        <v>67.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="M10" t="n">
-        <v>64.2</v>
+        <v>49.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
         <v>40</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.5</v>
+        <v>-3</v>
       </c>
       <c r="R10" t="n">
-        <v>-2</v>
+        <v>3.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4</v>
+        <v>4.3</v>
       </c>
       <c r="U10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>8.0 (5g)</t>
+          <t>2.0 (5g)</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1306,79 +1306,79 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="E11" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="H11" t="n">
-        <v>11.3</v>
+        <v>7.1</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>26.5</v>
       </c>
       <c r="K11" t="n">
-        <v>22.7</v>
+        <v>27.9</v>
       </c>
       <c r="L11" t="n">
-        <v>52.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>50.1</v>
+        <v>64.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>40</v>
       </c>
       <c r="P11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.8</v>
+        <v>-2</v>
       </c>
       <c r="S11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>20</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>8.0 (5g)</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>21</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>10.6 (5g)</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
-        <v>16.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,73 +1388,73 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>10.2</v>
       </c>
       <c r="G12" t="n">
-        <v>20.6</v>
+        <v>9.9</v>
       </c>
       <c r="H12" t="n">
-        <v>20.7</v>
+        <v>11.3</v>
       </c>
       <c r="I12" t="n">
-        <v>20.1</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>27.9</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>28.2</v>
+        <v>22.7</v>
       </c>
       <c r="L12" t="n">
-        <v>43.4</v>
+        <v>52.3</v>
       </c>
       <c r="M12" t="n">
-        <v>40.6</v>
+        <v>50.1</v>
       </c>
       <c r="N12" t="n">
         <v>5.3</v>
       </c>
       <c r="O12" t="n">
+        <v>40</v>
+      </c>
+      <c r="P12" t="n">
         <v>60</v>
       </c>
-      <c r="P12" t="n">
-        <v>53</v>
-      </c>
       <c r="Q12" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.1</v>
+        <v>-0.8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>25.5 (4g)</t>
+          <t>10.6 (5g)</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="13">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="E13" t="n">
         <v>15.3</v>
@@ -1507,13 +1507,13 @@
         <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P13" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.7</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
         <v>-1</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
@@ -1751,7 +1751,7 @@
         <v>40</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.7</v>
+        <v>-0.7</v>
       </c>
       <c r="R16" t="n">
         <v>2.6</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
@@ -1827,13 +1827,13 @@
         <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1</v>
+        <v>-0.1</v>
       </c>
       <c r="R17" t="n">
         <v>0.4</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="E25" t="n">
         <v>26</v>
@@ -2462,10 +2462,10 @@
         <v>50</v>
       </c>
       <c r="P25" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R25" t="n">
         <v>-3.5</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="E32" t="n">
         <v>8</v>
@@ -3025,13 +3025,13 @@
         <v>5.2</v>
       </c>
       <c r="O32" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P32" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="R32" t="n">
         <v>-4.9</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="E41" t="n">
         <v>9</v>
@@ -3747,13 +3747,13 @@
         <v>4.9</v>
       </c>
       <c r="O41" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P41" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R41" t="n">
         <v>2</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="n">
         <v>11</v>
@@ -3829,13 +3829,13 @@
         <v>7.8</v>
       </c>
       <c r="O42" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P42" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="R42" t="n">
         <v>-0.5</v>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="n">
         <v>18</v>
@@ -4567,13 +4567,13 @@
         <v>9.6</v>
       </c>
       <c r="O51" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P51" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q51" t="n">
-        <v>-4.4</v>
+        <v>-3.4</v>
       </c>
       <c r="R51" t="n">
         <v>7.3</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E54" t="n">
         <v>16.3</v>
@@ -4809,13 +4809,13 @@
         <v>11</v>
       </c>
       <c r="O54" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P54" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q54" t="n">
-        <v>-4.4</v>
+        <v>-3.4</v>
       </c>
       <c r="R54" t="n">
         <v>6.3</v>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="E61" t="n">
         <v>16.3</v>
@@ -5383,13 +5383,13 @@
         <v>4.8</v>
       </c>
       <c r="O61" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P61" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="R61" t="n">
         <v>-1.8</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E62" t="n">
         <v>23.7</v>
@@ -5465,13 +5465,13 @@
         <v>7.5</v>
       </c>
       <c r="O62" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="Q62" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="R62" t="n">
         <v>6.3</v>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="E66" t="n">
         <v>24.7</v>
@@ -5799,7 +5799,7 @@
         <v>33</v>
       </c>
       <c r="Q66" t="n">
-        <v>-1</v>
+        <v>-0</v>
       </c>
       <c r="R66" t="n">
         <v>4.1</v>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="E71" t="n">
         <v>17.7</v>
@@ -6209,7 +6209,7 @@
         <v>47</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="R71" t="n">
         <v>-5.3</v>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E76" t="n">
         <v>11.3</v>
@@ -6593,13 +6593,13 @@
         <v>5.1</v>
       </c>
       <c r="O76" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P76" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q76" t="n">
-        <v>-2.9</v>
+        <v>-1.9</v>
       </c>
       <c r="R76" t="n">
         <v>2.8</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E85" t="n">
         <v>6.7</v>
@@ -7314,10 +7314,10 @@
         <v>50</v>
       </c>
       <c r="P85" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="R85" t="n">
         <v>-2.7</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="E86" t="n">
         <v>10.3</v>
@@ -7396,10 +7396,10 @@
         <v>50</v>
       </c>
       <c r="P86" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q86" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R86" t="n">
         <v>-8.4</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E91" t="n">
         <v>3.7</v>
@@ -7794,10 +7794,10 @@
         <v>40</v>
       </c>
       <c r="P91" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R91" t="n">
         <v>-4</v>
@@ -7986,7 +7986,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8003,72 +8003,68 @@
         <v>14.5</v>
       </c>
       <c r="E94" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="F94" t="n">
-        <v>16</v>
+        <v>15.4</v>
       </c>
       <c r="G94" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
       </c>
       <c r="H94" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="I94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J94" t="n">
-        <v>25.5</v>
+        <v>22.1</v>
       </c>
       <c r="K94" t="n">
-        <v>23.5</v>
+        <v>22.6</v>
       </c>
       <c r="L94" t="n">
-        <v>42.8</v>
+        <v>46.6</v>
       </c>
       <c r="M94" t="n">
-        <v>43</v>
+        <v>41.4</v>
       </c>
       <c r="N94" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="O94" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P94" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="Q94" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T94" t="n">
         <v>-0.5</v>
       </c>
-      <c r="R94" t="n">
-        <v>2</v>
-      </c>
-      <c r="S94" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="T94" t="n">
-        <v>2</v>
-      </c>
       <c r="U94" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V94" t="n">
-        <v>6</v>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>15.4 (5g)</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="W94" t="inlineStr"/>
       <c r="X94" t="n">
-        <v>-6.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8082,71 +8078,75 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="E95" t="n">
-        <v>14.3</v>
+        <v>27.7</v>
       </c>
       <c r="F95" t="n">
-        <v>15.4</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>12.9</v>
+        <v>22.2</v>
       </c>
       <c r="H95" t="n">
-        <v>12.7</v>
+        <v>18.4</v>
       </c>
       <c r="I95" t="n">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="J95" t="n">
-        <v>22.1</v>
+        <v>32</v>
       </c>
       <c r="K95" t="n">
-        <v>22.6</v>
+        <v>28.8</v>
       </c>
       <c r="L95" t="n">
-        <v>46.6</v>
+        <v>50.5</v>
       </c>
       <c r="M95" t="n">
-        <v>41.4</v>
+        <v>45.9</v>
       </c>
       <c r="N95" t="n">
-        <v>5.1</v>
+        <v>13.7</v>
       </c>
       <c r="O95" t="n">
+        <v>60</v>
+      </c>
+      <c r="P95" t="n">
         <v>30</v>
       </c>
-      <c r="P95" t="n">
-        <v>27</v>
-      </c>
       <c r="Q95" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="R95" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="S95" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="T95" t="n">
-        <v>-0.5</v>
+        <v>3.3</v>
       </c>
       <c r="U95" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V95" t="n">
-        <v>15</v>
-      </c>
-      <c r="W95" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>17.8 (6g)</t>
+        </is>
+      </c>
       <c r="X95" t="n">
-        <v>6.2</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8160,55 +8160,55 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="n">
-        <v>27.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>10.2</v>
       </c>
       <c r="G96" t="n">
-        <v>22.2</v>
+        <v>11</v>
       </c>
       <c r="H96" t="n">
-        <v>18.4</v>
+        <v>11.1</v>
       </c>
       <c r="I96" t="n">
-        <v>18.3</v>
+        <v>11.2</v>
       </c>
       <c r="J96" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="K96" t="n">
-        <v>28.8</v>
+        <v>31.6</v>
       </c>
       <c r="L96" t="n">
-        <v>50.5</v>
+        <v>41.6</v>
       </c>
       <c r="M96" t="n">
-        <v>45.9</v>
+        <v>40.5</v>
       </c>
       <c r="N96" t="n">
-        <v>13.7</v>
+        <v>4.7</v>
       </c>
       <c r="O96" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P96" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q96" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="R96" t="n">
-        <v>1.7</v>
+        <v>-1</v>
       </c>
       <c r="S96" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="T96" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="U96" t="n">
         <v>23</v>
@@ -8216,19 +8216,15 @@
       <c r="V96" t="n">
         <v>6</v>
       </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>17.8 (6g)</t>
-        </is>
-      </c>
+      <c r="W96" t="inlineStr"/>
       <c r="X96" t="n">
-        <v>-6.8</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8238,75 +8234,79 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.5</v>
+        <v>21.5</v>
       </c>
       <c r="E97" t="n">
-        <v>9.699999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="F97" t="n">
-        <v>10.2</v>
+        <v>19.6</v>
       </c>
       <c r="G97" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H97" t="n">
-        <v>11.1</v>
+        <v>20.4</v>
       </c>
       <c r="I97" t="n">
-        <v>11.2</v>
+        <v>20.5</v>
       </c>
       <c r="J97" t="n">
-        <v>32.8</v>
+        <v>30.6</v>
       </c>
       <c r="K97" t="n">
-        <v>31.6</v>
+        <v>30.7</v>
       </c>
       <c r="L97" t="n">
-        <v>41.6</v>
+        <v>71.5</v>
       </c>
       <c r="M97" t="n">
-        <v>40.5</v>
+        <v>63</v>
       </c>
       <c r="N97" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O97" t="n">
         <v>40</v>
       </c>
       <c r="P97" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q97" t="n">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
       <c r="R97" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="S97" t="n">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="T97" t="n">
-        <v>1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="U97" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="V97" t="n">
-        <v>6</v>
-      </c>
-      <c r="W97" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>28.5 (4g)</t>
+        </is>
+      </c>
       <c r="X97" t="n">
-        <v>-11.2</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8316,41 +8316,41 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="E98" t="n">
-        <v>18.3</v>
+        <v>12.7</v>
       </c>
       <c r="F98" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G98" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I98" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J98" t="n">
         <v>19.6</v>
       </c>
-      <c r="G98" t="n">
-        <v>20</v>
-      </c>
-      <c r="H98" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I98" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J98" t="n">
-        <v>30.6</v>
-      </c>
       <c r="K98" t="n">
-        <v>30.7</v>
+        <v>22.2</v>
       </c>
       <c r="L98" t="n">
-        <v>71.5</v>
+        <v>39.1</v>
       </c>
       <c r="M98" t="n">
-        <v>63</v>
+        <v>42.7</v>
       </c>
       <c r="N98" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O98" t="n">
         <v>40</v>
@@ -8359,36 +8359,32 @@
         <v>40</v>
       </c>
       <c r="Q98" t="n">
-        <v>-1</v>
+        <v>-1.6</v>
       </c>
       <c r="R98" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="S98" t="n">
-        <v>8.5</v>
+        <v>-3.6</v>
       </c>
       <c r="T98" t="n">
-        <v>-0.1</v>
+        <v>-2.6</v>
       </c>
       <c r="U98" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="V98" t="n">
         <v>15</v>
       </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>28.5 (4g)</t>
-        </is>
-      </c>
+      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
-        <v>11.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8398,75 +8394,75 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="E99" t="n">
-        <v>12.7</v>
+        <v>17.3</v>
       </c>
       <c r="F99" t="n">
-        <v>10.8</v>
+        <v>17.4</v>
       </c>
       <c r="G99" t="n">
-        <v>9.1</v>
+        <v>17.9</v>
       </c>
       <c r="H99" t="n">
-        <v>8.800000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="I99" t="n">
-        <v>9.9</v>
+        <v>19.7</v>
       </c>
       <c r="J99" t="n">
-        <v>19.6</v>
+        <v>32.7</v>
       </c>
       <c r="K99" t="n">
-        <v>22.2</v>
+        <v>32.7</v>
       </c>
       <c r="L99" t="n">
-        <v>39.1</v>
+        <v>44.7</v>
       </c>
       <c r="M99" t="n">
-        <v>42.7</v>
+        <v>44.7</v>
       </c>
       <c r="N99" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="O99" t="n">
         <v>30</v>
       </c>
       <c r="P99" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q99" t="n">
-        <v>-2.6</v>
+        <v>0.2</v>
       </c>
       <c r="R99" t="n">
-        <v>0.9</v>
+        <v>-2.3</v>
       </c>
       <c r="S99" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>-2.6</v>
+        <v>-0</v>
       </c>
       <c r="U99" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="V99" t="n">
         <v>15</v>
       </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
-        <v>-0.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8480,71 +8476,71 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="E100" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F100" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H100" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J100" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K100" t="n">
         <v>17.3</v>
       </c>
-      <c r="F100" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G100" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="H100" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I100" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="J100" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="K100" t="n">
-        <v>32.7</v>
-      </c>
       <c r="L100" t="n">
-        <v>44.7</v>
+        <v>38.6</v>
       </c>
       <c r="M100" t="n">
-        <v>44.7</v>
+        <v>32.2</v>
       </c>
       <c r="N100" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P100" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.2</v>
+        <v>-4.8</v>
       </c>
       <c r="R100" t="n">
-        <v>-2.3</v>
+        <v>4.7</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="T100" t="n">
-        <v>-0</v>
+        <v>3.5</v>
       </c>
       <c r="U100" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V100" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="n">
-        <v>8.699999999999999</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8554,75 +8550,79 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="E101" t="n">
-        <v>11.7</v>
+        <v>7</v>
       </c>
       <c r="F101" t="n">
-        <v>13.4</v>
+        <v>5</v>
       </c>
       <c r="G101" t="n">
-        <v>11.8</v>
+        <v>5.5</v>
       </c>
       <c r="H101" t="n">
-        <v>11.3</v>
+        <v>5.3</v>
       </c>
       <c r="I101" t="n">
-        <v>8.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="J101" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="K101" t="n">
-        <v>17.3</v>
+        <v>21.1</v>
       </c>
       <c r="L101" t="n">
-        <v>38.6</v>
+        <v>48.6</v>
       </c>
       <c r="M101" t="n">
-        <v>32.2</v>
+        <v>54.5</v>
       </c>
       <c r="N101" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="O101" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P101" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q101" t="n">
-        <v>-3.8</v>
+        <v>-0.8</v>
       </c>
       <c r="R101" t="n">
-        <v>4.7</v>
+        <v>-0.7</v>
       </c>
       <c r="S101" t="n">
-        <v>6.4</v>
+        <v>-5.9</v>
       </c>
       <c r="T101" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="U101" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="V101" t="n">
-        <v>6</v>
-      </c>
-      <c r="W101" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>5.5 (6g)</t>
+        </is>
+      </c>
       <c r="X101" t="n">
-        <v>4.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8632,79 +8632,79 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="E102" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F102" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G102" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H102" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I102" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J102" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K102" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="M102" t="n">
+        <v>52</v>
+      </c>
+      <c r="N102" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O102" t="n">
+        <v>50</v>
+      </c>
+      <c r="P102" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="R102" t="n">
         <v>5</v>
       </c>
-      <c r="G102" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H102" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I102" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J102" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K102" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="L102" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="M102" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="N102" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O102" t="n">
-        <v>30</v>
-      </c>
-      <c r="P102" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R102" t="n">
-        <v>-0.7</v>
-      </c>
       <c r="S102" t="n">
-        <v>-5.9</v>
+        <v>5.6</v>
       </c>
       <c r="T102" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="U102" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="V102" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>5.5 (6g)</t>
+          <t>13.0 (3g)</t>
         </is>
       </c>
       <c r="X102" t="n">
-        <v>-0.3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8718,75 +8718,75 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
       <c r="E103" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F103" t="n">
-        <v>17.6</v>
+        <v>9</v>
       </c>
       <c r="G103" t="n">
-        <v>16.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H103" t="n">
-        <v>16.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>12.6</v>
+        <v>9</v>
       </c>
       <c r="J103" t="n">
-        <v>31.8</v>
+        <v>29.8</v>
       </c>
       <c r="K103" t="n">
-        <v>27.1</v>
+        <v>29.7</v>
       </c>
       <c r="L103" t="n">
-        <v>57.6</v>
+        <v>37.2</v>
       </c>
       <c r="M103" t="n">
-        <v>52</v>
+        <v>37.8</v>
       </c>
       <c r="N103" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="O103" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P103" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="Q103" t="n">
-        <v>-1.9</v>
+        <v>-0.5</v>
       </c>
       <c r="R103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>5.6</v>
+        <v>-0.6</v>
       </c>
       <c r="T103" t="n">
-        <v>4.8</v>
+        <v>0.1</v>
       </c>
       <c r="U103" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="V103" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>13.0 (3g)</t>
+          <t>9.0 (3g)</t>
         </is>
       </c>
       <c r="X103" t="n">
-        <v>10.3</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8796,79 +8796,75 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>12.3</v>
       </c>
       <c r="F104" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="G104" t="n">
-        <v>9.300000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="H104" t="n">
-        <v>9.300000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="I104" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J104" t="n">
-        <v>29.8</v>
+        <v>32.7</v>
       </c>
       <c r="K104" t="n">
-        <v>29.7</v>
+        <v>30.2</v>
       </c>
       <c r="L104" t="n">
-        <v>37.2</v>
+        <v>57.5</v>
       </c>
       <c r="M104" t="n">
-        <v>37.8</v>
+        <v>59.4</v>
       </c>
       <c r="N104" t="n">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="O104" t="n">
         <v>60</v>
       </c>
       <c r="P104" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q104" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="S104" t="n">
-        <v>-0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="T104" t="n">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="U104" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="V104" t="n">
-        <v>15</v>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>9.0 (3g)</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
-        <v>-10.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8878,75 +8874,79 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>14.5</v>
+        <v>21.5</v>
       </c>
       <c r="E105" t="n">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="F105" t="n">
-        <v>12.6</v>
+        <v>19</v>
       </c>
       <c r="G105" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="H105" t="n">
-        <v>16.6</v>
+        <v>21.1</v>
       </c>
       <c r="I105" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="L105" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="M105" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="N105" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O105" t="n">
+        <v>50</v>
+      </c>
+      <c r="P105" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R105" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U105" t="n">
+        <v>16</v>
+      </c>
+      <c r="V105" t="n">
         <v>15</v>
       </c>
-      <c r="J105" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="K105" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="L105" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="M105" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="N105" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O105" t="n">
-        <v>60</v>
-      </c>
-      <c r="P105" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R105" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="S105" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="T105" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U105" t="n">
-        <v>25</v>
-      </c>
-      <c r="V105" t="n">
-        <v>6</v>
-      </c>
-      <c r="W105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>20.0 (6g)</t>
+        </is>
+      </c>
       <c r="X105" t="n">
-        <v>3</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8956,73 +8956,69 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>21.5</v>
+        <v>4.5</v>
       </c>
       <c r="E106" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>19</v>
+        <v>3.4</v>
       </c>
       <c r="G106" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H106" t="n">
-        <v>21.1</v>
+        <v>5.2</v>
       </c>
       <c r="I106" t="n">
-        <v>22.1</v>
+        <v>5.4</v>
       </c>
       <c r="J106" t="n">
-        <v>36.2</v>
+        <v>17</v>
       </c>
       <c r="K106" t="n">
-        <v>35.5</v>
+        <v>20.9</v>
       </c>
       <c r="L106" t="n">
-        <v>43.7</v>
+        <v>51.3</v>
       </c>
       <c r="M106" t="n">
-        <v>44.4</v>
+        <v>57.4</v>
       </c>
       <c r="N106" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="O106" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P106" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="R106" t="n">
-        <v>-3.1</v>
+        <v>-2</v>
       </c>
       <c r="S106" t="n">
-        <v>-0.7</v>
+        <v>-6.1</v>
       </c>
       <c r="T106" t="n">
-        <v>0.7</v>
+        <v>-3.8</v>
       </c>
       <c r="U106" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="V106" t="n">
-        <v>15</v>
-      </c>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>20.0 (6g)</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="W106" t="inlineStr"/>
       <c r="X106" t="n">
-        <v>-4.9</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -9141,10 +9137,10 @@
         <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.345</v>
+        <v>1.364</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -9189,10 +9185,10 @@
         <v>0.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -9203,7 +9199,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9213,45 +9209,45 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.506</v>
+        <v>0.585</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="K4" t="n">
-        <v>1.357</v>
+        <v>1.4</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Low scoring variance (σ=3.7) — highly predictable output near line — marginally supports the lean OVER. FG% +4.6% trending (L10 vs L30). Opponent is strong defense (#9) at slow pace (#21). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 7.7 pts (0.2 pts above line; 50% blended confidence [T3_LEAN]).</t>
+          <t>Ball averages 25.5 pts in 4 meetings (+6.0 vs line) — supports the OVER. H2H avg 5.4 pts above season L30. Opponent is below-average defense (#22) at above-average pace (#12). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 22.3 pts (2.8 pts above line; 58% blended confidence [T2]). Risk: L3 has dropped to 16.0 (4.1 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9261,28 +9257,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.623</v>
+        <v>0.506</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>22.5</v>
+        <v>7.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -9292,14 +9288,14 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Knueppel averages 24.7 pts in 3 meetings (+7.2 vs line) — supports the OVER. H2H avg 5.8 pts above season L30; TS% shifts +6.7% in this matchup. Opponent is below-average defense (#22) at above-average pace (#12). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 22.5 pts (5.0 pts above line; 62% blended confidence [T2]). Risk: L3 has dropped to 13.7 (5.2 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>[Low conviction — lean only] Low scoring variance (σ=3.7) — highly predictable output near line — marginally supports the lean OVER. FG% +4.6% trending (L10 vs L30). Opponent is strong defense (#9) at slow pace (#21). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 7.7 pts (0.2 pts above line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9309,45 +9305,45 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.624</v>
+        <v>0.623</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J6" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.455</v>
+        <v>1.385</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Toppin averages 6.0 pts in 4 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 4.8 pts below season L30; TS% shifts -19.2% in this matchup. Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 5.0 pts (4.5 pts below line; 62% blended confidence [T3]).</t>
+          <t>Knueppel averages 24.7 pts in 3 meetings (+7.2 vs line) — supports the OVER. H2H avg 5.8 pts above season L30; TS% shifts +6.7% in this matchup. Opponent is below-average defense (#22) at above-average pace (#12). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 22.5 pts (5.0 pts above line; 62% blended confidence [T2]). Risk: L3 has dropped to 13.7 (5.2 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9357,45 +9353,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="K7" t="n">
-        <v>1.385</v>
+        <v>1.455</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Miller averages 23.5 pts in 4 meetings (+4.0 vs line) — supports the OVER. H2H avg 3.2 pts above season L30; TS% shifts +11.4% in this matchup. Opponent is below-average defense (#20) at above-average pace (#12). 8/10 signals agree — Volume, HR L30, Trend, Context support the OVER; HR L10, Min Trend dissent. Projection model targets 21.0 pts (1.5 pts above line; 55% blended confidence [T2]).</t>
+          <t>Toppin averages 6.0 pts in 4 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 4.8 pts below season L30; TS% shifts -19.2% in this matchup. Opponent is strong defense (#8) at slow pace (#21). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 5.0 pts (4.5 pts below line; 62% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9405,28 +9401,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.573</v>
+        <v>0.516</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>20.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>2.9</v>
@@ -9436,14 +9432,14 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Bridges averages 17.2 pts in 4 meetings (+2.7 vs line) — marginally supports the UNDER. H2H avg 2.6 pts above season L30; TS% shifts +9.1% in this matchup. Opponent is below-average defense (#20) at above-average pace (#12). Mixed signals: 4/10 agree (HR L30, HR L10, Context); counter-signals: Volume, Trend, Defense. Projection model targets 12.0 pts (2.5 pts below line; 57% blended confidence [T3]). Risk: L3 has surged to 19.3 after a 6-pt outing (4.7 above L30) — momentum could push over the under line.</t>
+          <t>[Low conviction — lean only] Miller averages 23.5 pts in 4 meetings (+3.0 vs line) — supports the lean OVER. H2H avg 3.2 pts above season L30; TS% shifts +11.4% in this matchup. Opponent is below-average defense (#20) at above-average pace (#12). 7/10 signals agree — HR L30, Trend, Context, Defense support the OVER; Volume, HR L10, Min Trend dissent. Projection model targets 20.7 pts (0.2 pts above line; 51% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9458,40 +9454,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.669</v>
+        <v>0.573</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>1.435</v>
+        <v>1.4</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brown averages 2.0 pts in 5 meetings (-8.5 vs line) — supports the UNDER. H2H avg 5.5 pts below season L30; TS% shifts -6.8% in this matchup. Opponent is strong defense (#8) at slow pace (#21). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 4.8 pts (5.7 pts below line; 66% blended confidence [T1_PREMIUM]). Risk: L3 has surged to 15.3 after a 12-pt outing (7.8 above L30) — momentum could push over the under line.</t>
+          <t>Bridges averages 17.2 pts in 4 meetings (+2.7 vs line) — marginally supports the UNDER. H2H avg 2.6 pts above season L30; TS% shifts +9.1% in this matchup. Opponent is below-average defense (#20) at above-average pace (#12). Mixed signals: 4/10 agree (HR L30, HR L10, Context); counter-signals: Volume, Trend, Defense. Projection model targets 12.0 pts (2.5 pts below line; 57% blended confidence [T3]). Risk: L3 has surged to 19.3 after a 6-pt outing (4.7 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9506,40 +9502,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.536</v>
+        <v>0.669</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.385</v>
+        <v>1.417</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.0 pts (L5 vs L30) — supports the UNDER. Opponent is below-average defense (#20) at above-average pace (#12). 6/10 signals agree — Volume, HR L10, Trend, Context support the UNDER; HR L30, Defense, Pace dissent. Projection model targets 7.3 pts (1.2 pts below line; 53% blended confidence [T3]).</t>
+          <t>Brown averages 2.0 pts in 5 meetings (-8.5 vs line) — supports the UNDER. H2H avg 5.5 pts below season L30; TS% shifts -6.8% in this matchup. Opponent is strong defense (#8) at slow pace (#21). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 4.8 pts (5.7 pts below line; 66% blended confidence [T1_PREMIUM]). Risk: L3 has surged to 15.3 after a 12-pt outing (7.8 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9549,7 +9545,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9558,36 +9554,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.572</v>
+        <v>0.536</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>12.1</v>
+        <v>7.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="K11" t="n">
-        <v>1.408</v>
+        <v>1.4</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Huff's L30 average of 11.0 pts vs the 9.5 line — marginally supports the OVER. TS% shifts +16.3% in this matchup. Opponent is elite defense (#4) at slow pace (#21). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.1 pts (2.6 pts above line; 57% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 2.0 pts (L5 vs L30) — supports the UNDER. Opponent is below-average defense (#20) at above-average pace (#12). 6/10 signals agree — Volume, HR L10, Trend, Context support the UNDER; HR L30, Defense, Pace dissent. Projection model targets 7.3 pts (1.2 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9602,23 +9598,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.585</v>
+        <v>0.572</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>22.3</v>
+        <v>12.1</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>2.9</v>
@@ -9628,7 +9624,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Ball averages 25.5 pts in 4 meetings (+6.0 vs line) — supports the OVER. H2H avg 5.4 pts above season L30. Opponent is below-average defense (#22) at above-average pace (#12). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 22.3 pts (2.8 pts above line; 58% blended confidence [T2]). Risk: L3 has dropped to 16.0 (4.1 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Huff's L30 average of 11.0 pts vs the 9.5 line — marginally supports the OVER. TS% shifts +16.3% in this matchup. Opponent is elite defense (#4) at slow pace (#21). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.1 pts (2.6 pts above line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -9654,29 +9650,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.518</v>
+        <v>0.605</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.833</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.909</v>
+        <v>1.385</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>White's L30 average of 16.8 pts vs the 17.5 line — marginally supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts -4.0% in this matchup. Opponent is below-average defense (#22) at above-average pace (#12). Mixed signals: 5/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 18.2 pts (0.7 pts above line; 51% blended confidence [T3]). Risk: minutes trending down (20.9 L10 vs 24.5 L30) — role reduction would suppress counting stats.</t>
+          <t>White averages 19.4 pts in 7 meetings (+3.9 vs line) — supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts -4.0% in this matchup. Opponent is below-average defense (#22) at above-average pace (#12). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 18.5 pts (3.0 pts above line; 60% blended confidence [T3]). Risk: minutes trending down (20.9 L10 vs 24.5 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -9717,10 +9713,10 @@
         <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2.04</v>
+        <v>1.769</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -9765,10 +9761,10 @@
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="K15" t="n">
-        <v>1.385</v>
+        <v>1.455</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
@@ -9798,10 +9794,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.574</v>
+        <v>0.543</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -9810,17 +9806,17 @@
         <v>9.9</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.962</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1.758</v>
+        <v>1.599</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.6 pts (L5 vs L30) — supports the UNDER. TS% shifts +18.1% in this matchup; FG% -3.8% trending (L10 vs L30). Opponent is below-average defense (#16) at slow pace (#23). 6/10 signals agree — Volume, HR L30, Context, H2H support the UNDER; HR L10, Trend, Defense dissent. Projection model targets 9.9 pts (2.6 pts below line; 57% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 2.6 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +18.1% in this matchup; FG% -3.8% trending (L10 vs L30). Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.9 pts (1.6 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -9846,10 +9842,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.55</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -9858,7 +9854,7 @@
         <v>14.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>1.775</v>
@@ -9868,7 +9864,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.0) — highly predictable output near line — marginally supports the OVER. Opponent is average defense (#15) at slow pace (#23). Mixed signals: 1/10 agree (Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.6 pts (1.1 pts above line; 55% blended confidence [T3]). Risk: only 33% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Low scoring variance (σ=4.0) — highly predictable output near line — marginally supports the OVER. Opponent is average defense (#15) at slow pace (#23). Mixed signals: 2/10 agree (Trend, Context); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.6 pts (2.1 pts above line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -9909,10 +9905,10 @@
         <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.333</v>
+        <v>1.364</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -10101,10 +10097,10 @@
         <v>7.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -10149,10 +10145,10 @@
         <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>1.345</v>
+        <v>1.357</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -10230,7 +10226,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.554</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
@@ -10242,7 +10238,7 @@
         <v>22.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.15</v>
@@ -10252,7 +10248,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.5 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +8.9% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 3/10 agree (Trend, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 22.8 pts (2.7 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=10.3) makes the outcome difficult to call with confidence.</t>
+          <t>Edwards's L30 of 29.1 pts sits 4.6 above the 24.5 line — marginally supports the UNDER. TS% shifts +8.9% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 3/10 agree (Trend, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 22.8 pts (1.7 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=10.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -10293,10 +10289,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -10389,10 +10385,10 @@
         <v>0.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>1.4</v>
+        <v>1.357</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -10437,10 +10433,10 @@
         <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.417</v>
+        <v>1.345</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -10533,10 +10529,10 @@
         <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>1.4</v>
+        <v>1.357</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -10566,10 +10562,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.547</v>
+        <v>0.584</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -10578,17 +10574,17 @@
         <v>7.7</v>
       </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.9 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 2.3 pts below season L30; TS% shifts +4.3% in this matchup. Opponent is weak defense (#24) at above-average pace (#7). Mixed signals: 4/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.7 pts (1.8 pts below line; 54% blended confidence [T3]). Risk: minutes trending down (21.4 L10 vs 25.6 L30) — role reduction would suppress counting stats.</t>
+          <t>Recent scoring trending down 4.9 pts (L5 vs L30) — supports the UNDER. H2H avg 2.3 pts below season L30; TS% shifts +4.3% in this matchup. Opponent is weak defense (#24) at above-average pace (#7). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, Pace dissent. Projection model targets 7.7 pts (2.8 pts below line; 58% blended confidence [T3]). Risk: minutes trending down (21.4 L10 vs 25.6 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -10629,10 +10625,10 @@
         <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.4</v>
+        <v>1.357</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -10677,10 +10673,10 @@
         <v>11.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="K34" t="n">
-        <v>1.465</v>
+        <v>1.357</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -10725,10 +10721,10 @@
         <v>0.4</v>
       </c>
       <c r="J35" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="K35" t="n">
-        <v>1.417</v>
+        <v>1.435</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
@@ -10821,10 +10817,10 @@
         <v>2.5</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K37" t="n">
-        <v>1.364</v>
+        <v>1.435</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -10869,10 +10865,10 @@
         <v>2.8</v>
       </c>
       <c r="J38" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K38" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
@@ -10917,10 +10913,10 @@
         <v>2.9</v>
       </c>
       <c r="J39" t="n">
-        <v>1.833</v>
+        <v>2.75</v>
       </c>
       <c r="K39" t="n">
-        <v>1.909</v>
+        <v>1.417</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
@@ -10965,10 +10961,10 @@
         <v>4.1</v>
       </c>
       <c r="J40" t="n">
-        <v>1.699</v>
+        <v>2.9</v>
       </c>
       <c r="K40" t="n">
-        <v>2.06</v>
+        <v>1.385</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -10994,33 +10990,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.533</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>10.7</v>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K41" t="n">
-        <v>1.741</v>
+        <v>1.408</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.0 pts (L5 vs L30) — marginally supports the OVER. Opponent is strong defense (#8) at slow pace (#27). Mixed signals: 5/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 10.7 pts (1.2 pts above line; 53% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 2.0 pts (L5 vs L30) — supports the OVER. Opponent is strong defense (#8) at slow pace (#27). 7/10 signals agree — Volume, HR L30, Trend, Context support the OVER; HR L10, Defense, Pace dissent. Projection model targets 10.7 pts (2.2 pts above line; 56% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -11042,33 +11038,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.702</v>
+        <v>0.668</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>5.7</v>
       </c>
       <c r="I42" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="K42" t="n">
-        <v>1.87</v>
+        <v>1.455</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Hart averages 6.6 pts in 5 meetings (-6.9 vs line) — supports the UNDER. H2H avg 5.7 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is below-average defense (#18) at fast pace (#1). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, FG Trend dissent. Projection model targets 5.7 pts (7.8 pts below line; 70% blended confidence [T2]). Risk: high variance (σ=7.8) makes the outcome difficult to call with confidence.</t>
+          <t>Hart averages 6.6 pts in 5 meetings (-5.9 vs line) — marginally supports the UNDER. H2H avg 5.7 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is below-average defense (#18) at fast pace (#1). Mixed signals: 5/10 agree (Volume, HR L30, Trend); counter-signals: HR L10, Defense, Pace. Projection model targets 5.7 pts (6.8 pts below line; 66% blended confidence [T3]). Risk: high variance (σ=7.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -11109,10 +11105,10 @@
         <v>1.6</v>
       </c>
       <c r="J43" t="n">
-        <v>1.833</v>
+        <v>2.9</v>
       </c>
       <c r="K43" t="n">
-        <v>1.909</v>
+        <v>1.385</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -11157,10 +11153,10 @@
         <v>1.5</v>
       </c>
       <c r="J44" t="n">
-        <v>1.833</v>
+        <v>2.75</v>
       </c>
       <c r="K44" t="n">
-        <v>1.909</v>
+        <v>1.417</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11201,10 @@
         <v>4.6</v>
       </c>
       <c r="J45" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="K45" t="n">
-        <v>1.87</v>
+        <v>1.408</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
@@ -11253,10 +11249,10 @@
         <v>2.2</v>
       </c>
       <c r="J46" t="n">
-        <v>1.952</v>
+        <v>3.1</v>
       </c>
       <c r="K46" t="n">
-        <v>1.8</v>
+        <v>1.345</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
@@ -11301,10 +11297,10 @@
         <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>1.952</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>1.8</v>
+        <v>1.357</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -11349,10 +11345,10 @@
         <v>0.8</v>
       </c>
       <c r="J48" t="n">
-        <v>1.833</v>
+        <v>3.1</v>
       </c>
       <c r="K48" t="n">
-        <v>1.909</v>
+        <v>1.345</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -11397,10 +11393,10 @@
         <v>2.1</v>
       </c>
       <c r="J49" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="K49" t="n">
-        <v>1.952</v>
+        <v>1.385</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -11478,7 +11474,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.584</v>
+        <v>0.546</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -11490,7 +11486,7 @@
         <v>11.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>2.9</v>
@@ -11500,7 +11496,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 7.3 pts (L5 vs L30) — supports the UNDER. FG% +3.1% trending (L10 vs L30); Minutes up 6.7 recently (L10=29.3 vs L30=22.6). Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 11.4 pts (2.1 pts below line; 58% blended confidence [T3]). Risk: L3 has surged to 18.0 (8.9 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending up 7.3 pts (L5 vs L30) — supports the UNDER. FG% +3.1% trending (L10 vs L30); Minutes up 6.7 recently (L10=29.3 vs L30=22.6). Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, H2H, FG Trend dissent. Projection model targets 11.4 pts (1.1 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 18.0 (8.9 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -11541,10 +11537,10 @@
         <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -11589,10 +11585,10 @@
         <v>0.1</v>
       </c>
       <c r="J53" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K53" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -11622,10 +11618,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.615</v>
+        <v>0.579</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -11634,7 +11630,7 @@
         <v>7.4</v>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>2.75</v>
@@ -11644,7 +11640,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 of 7.1 pts sits 4.4 below the 11.5 line — supports the UNDER. H2H avg 1.9 pts above season L30; TS% shifts +10.1% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 7.4 pts (4.1 pts below line; 61% blended confidence [T3]). Risk: L3 has surged to 16.3 after a 13-pt outing (9.2 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending up 6.3 pts (L5 vs L30) — supports the UNDER. H2H avg 1.9 pts above season L30; TS% shifts +10.1% in this matchup. Opponent is elite defense (#2) at slow pace (#24). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 7.4 pts (3.1 pts below line; 57% blended confidence [T3]). Risk: L3 has surged to 16.3 after a 13-pt outing (9.2 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -11733,10 +11729,10 @@
         <v>1.6</v>
       </c>
       <c r="J56" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K56" t="n">
-        <v>1.408</v>
+        <v>1.385</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
@@ -11781,10 +11777,10 @@
         <v>2.5</v>
       </c>
       <c r="J57" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K57" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
@@ -11877,10 +11873,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="K59" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
@@ -11958,29 +11954,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.522</v>
+        <v>0.544</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="K61" t="n">
-        <v>1.417</v>
+        <v>1.385</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.8) — highly predictable output near line — marginally supports the UNDER. H2H avg 1.7 pts below season L30; TS% shifts +3.6% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). Mixed signals: 4/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 17.0 pts (0.5 pts below line; 52% blended confidence [T3]).</t>
+          <t>Thompson averages 15.7 pts in 6 meetings (-2.8 vs line) — supports the UNDER. H2H avg 1.7 pts below season L30; TS% shifts +3.6% in this matchup. Opponent is weak defense (#30) at above-average pace (#8). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, FG Trend dissent. Projection model targets 16.9 pts (1.6 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -12006,10 +12002,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.61</v>
+        <v>0.572</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -12018,7 +12014,7 @@
         <v>13.5</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>3.05</v>
@@ -12028,7 +12024,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Filipowski averages 11.2 pts in 6 meetings (-5.3 vs line) — supports the UNDER. H2H avg 2.9 pts below season L30; TS% shifts -10.5% in this matchup. Opponent is strong defense (#7) at slow pace (#22). 8/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Min Trend dissent. Projection model targets 13.5 pts (3.0 pts below line; 60% blended confidence [T2]). Risk: L3 has surged to 23.7 after a 15-pt outing (9.6 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending up 6.3 pts (L5 vs L30) — supports the UNDER. H2H avg 2.9 pts below season L30; TS% shifts -10.5% in this matchup. Opponent is strong defense (#7) at slow pace (#22). 7/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, Min Trend dissent. Projection model targets 13.5 pts (2.0 pts below line; 57% blended confidence [T2]). Risk: L3 has surged to 23.7 after a 15-pt outing (9.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -12165,10 +12161,10 @@
         <v>0.4</v>
       </c>
       <c r="J65" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="K65" t="n">
-        <v>1.417</v>
+        <v>1.357</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -12198,10 +12194,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.578</v>
+        <v>0.61</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -12210,7 +12206,7 @@
         <v>23.5</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>2.75</v>
@@ -12220,7 +12216,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Sengun averages 24.8 pts in 6 meetings (+4.3 vs line) — supports the OVER. H2H avg 5.3 pts above season L30; TS% shifts +6.1% in this matchup. Opponent is below-average defense (#22) at above-average pace (#8). 6/10 signals agree — Trend, Defense, H2H, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 23.5 pts (3.0 pts above line; 57% blended confidence [T3]). Risk: high variance (σ=9.2) makes the outcome difficult to call with confidence.</t>
+          <t>Sengun averages 24.8 pts in 6 meetings (+5.3 vs line) — supports the OVER. H2H avg 5.3 pts above season L30; TS% shifts +6.1% in this matchup. Opponent is below-average defense (#22) at above-average pace (#8). 7/10 signals agree — Trend, Context, Defense, H2H support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 23.5 pts (4.0 pts above line; 61% blended confidence [T3]). Risk: high variance (σ=9.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -12309,10 +12305,10 @@
         <v>0.7</v>
       </c>
       <c r="J68" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K68" t="n">
-        <v>1.357</v>
+        <v>1.345</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
@@ -12357,10 +12353,10 @@
         <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K69" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -12405,10 +12401,10 @@
         <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="K70" t="n">
-        <v>1.435</v>
+        <v>1.345</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -12429,7 +12425,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -12438,29 +12434,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.503</v>
+        <v>0.524</v>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K71" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 5.3 pts (L5 vs L30) — supports the OVER. Opponent is weak defense (#23) at fast pace (#5). 6/10 signals agree — Volume, Context, Defense, Pace support the OVER; HR L30, HR L10, Trend dissent. Projection model targets 21.0 pts (0.5 pts above line; 50% blended confidence [T3]). Risk: high variance (σ=9.6) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 5.3 pts (L5 vs L30) — marginally supports the UNDER. Opponent is weak defense (#23) at fast pace (#5). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Defense, H2H, Pace. Projection model targets 20.5 pts (1.0 pts below line; 52% blended confidence [T3]). Risk: high variance (σ=9.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -12549,10 +12545,10 @@
         <v>2.4</v>
       </c>
       <c r="J73" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="K73" t="n">
-        <v>1.357</v>
+        <v>1.455</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
@@ -12597,10 +12593,10 @@
         <v>4.1</v>
       </c>
       <c r="J74" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K74" t="n">
-        <v>1.408</v>
+        <v>1.345</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
@@ -12645,10 +12641,10 @@
         <v>2.6</v>
       </c>
       <c r="J75" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K75" t="n">
-        <v>1.333</v>
+        <v>1.357</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
@@ -12669,19 +12665,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.519</v>
+        <v>0.532</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -12690,17 +12686,17 @@
         <v>8.5</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K76" t="n">
-        <v>1.435</v>
+        <v>1.364</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Shead's L30 of 5.6 pts sits 2.9 below the 8.5 line — marginally supports the lean UNDER. Minutes up 3.2 recently (L10=25.9 vs L30=22.7). Opponent is below-average defense (#22) at fast pace (#5). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 8.5 pts (0.0 pts below line; 51% blended confidence [T3_LEAN]). Risk: L3 has surged to 11.3 after a 12-pt outing (5.7 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending up 2.8 pts (L5 vs L30) — marginally supports the OVER. Minutes up 3.2 recently (L10=25.9 vs L30=22.7). Opponent is below-average defense (#22) at fast pace (#5). Mixed signals: 4/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.5 pts (1.0 pts above line; 53% blended confidence [T3]). Risk: only 27% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
@@ -12741,10 +12737,10 @@
         <v>2.6</v>
       </c>
       <c r="J77" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>1.357</v>
+        <v>1.364</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -12837,10 +12833,10 @@
         <v>3.2</v>
       </c>
       <c r="J79" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K79" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
@@ -12885,10 +12881,10 @@
         <v>2.1</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K80" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -12933,10 +12929,10 @@
         <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="K81" t="n">
-        <v>1.435</v>
+        <v>1.345</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
@@ -13029,10 +13025,10 @@
         <v>3.3</v>
       </c>
       <c r="J83" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K83" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -13101,16 +13097,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.511</v>
+        <v>0.543</v>
       </c>
       <c r="F85" t="n">
         <v>4</v>
@@ -13122,17 +13118,17 @@
         <v>10.7</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
-        <v>1.971</v>
+        <v>2.9</v>
       </c>
       <c r="K85" t="n">
-        <v>1.746</v>
+        <v>1.385</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Thompson averages 15.0 pts in 3 meetings (+4.5 vs line) — marginally supports the lean OVER. H2H avg 2.9 pts above season L30; TS% shifts +14.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 4/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 10.7 pts (0.2 pts above line; 51% blended confidence [T3_LEAN]). Risk: L3 has dropped to 6.7 (5.4 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Thompson averages 15.0 pts in 3 meetings (+5.5 vs line) — marginally supports the OVER. H2H avg 2.9 pts above season L30; TS% shifts +14.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 4/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 10.7 pts (1.2 pts above line; 54% blended confidence [T3]). Risk: L3 has dropped to 6.7 (5.4 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13154,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.597</v>
+        <v>0.62</v>
       </c>
       <c r="F86" t="n">
         <v>3</v>
@@ -13170,7 +13166,7 @@
         <v>11.6</v>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>2.9</v>
@@ -13180,7 +13176,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 8.4 pts (L5 vs L30) — marginally supports the UNDER. Minutes down 5.6 recently (L10=25.6 vs L30=31.2). Opponent is below-average defense (#19) at fast pace (#2). Mixed signals: 3/10 agree (Trend, FG Trend, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.6 pts (2.9 pts below line; 59% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 8.4 pts (L5 vs L30) — marginally supports the UNDER. Minutes down 5.6 recently (L10=25.6 vs L30=31.2). Opponent is below-average defense (#19) at fast pace (#2). Mixed signals: 3/10 agree (Trend, FG Trend, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.6 pts (3.9 pts below line; 61% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -13317,10 +13313,10 @@
         <v>0.5</v>
       </c>
       <c r="J89" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="K89" t="n">
-        <v>1.4</v>
+        <v>1.435</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
@@ -13365,10 +13361,10 @@
         <v>3.6</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K90" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
@@ -13398,10 +13394,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.604</v>
+        <v>0.571</v>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -13410,17 +13406,17 @@
         <v>6.7</v>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="K91" t="n">
-        <v>1.408</v>
+        <v>1.417</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.0 pts (L5 vs L30) — supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts +5.0% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 6/10 signals agree — HR L10, Trend, Context, H2H support the UNDER; Volume, HR L30, Defense dissent. Projection model targets 6.7 pts (3.8 pts below line; 60% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 4.0 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.3 pts below season L30; TS% shifts +5.0% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 5/10 agree (HR L10, Trend, H2H); counter-signals: Volume, HR L30, Context. Projection model targets 6.7 pts (2.8 pts below line; 57% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13519,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -13533,16 +13529,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.53</v>
+        <v>0.508</v>
       </c>
       <c r="F94" t="n">
         <v>5</v>
@@ -13551,27 +13547,27 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>13.1</v>
+        <v>14.5</v>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1.775</v>
+        <v>1.806</v>
       </c>
       <c r="K94" t="n">
-        <v>1.943</v>
+        <v>1.909</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.0 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts -6.2% in this matchup; Minutes up 2.0 recently (L10=25.5 vs L30=23.5). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 13.1 pts (1.4 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=9.8) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Fears's L30 of 12.0 pts sits 2.5 below the 14.5 line — marginally supports the lean UNDER. FG% +5.2% trending (L10 vs L30). Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 14.5 pts (0.0 pts below line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -13581,45 +13577,45 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.508</v>
+        <v>0.584</v>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
-        <v>1.826</v>
+        <v>1.599</v>
       </c>
       <c r="K95" t="n">
-        <v>1.893</v>
+        <v>2.2</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Fears's L30 of 12.0 pts sits 2.5 below the 14.5 line — marginally supports the lean UNDER. FG% +5.2% trending (L10 vs L30). Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 14.5 pts (0.0 pts below line; 50% blended confidence [T3_LEAN]).</t>
+          <t>DeRozan averages 17.8 pts in 6 meetings (-2.7 vs line) — marginally supports the UNDER. TS% shifts -6.8% in this matchup; FG% +4.6% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 16.5 pts (4.0 pts below line; 58% blended confidence [T3]). Risk: L3 has surged to 27.7 after a 20-pt outing (9.4 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -13638,36 +13634,36 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.573</v>
+        <v>0.543</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>16.5</v>
+        <v>11.2</v>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
-        <v>1.699</v>
+        <v>1.885</v>
       </c>
       <c r="K96" t="n">
-        <v>2.06</v>
+        <v>1.826</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>DeRozan's L30 average of 18.3 pts vs the 19.5 line — marginally supports the UNDER. TS% shifts -6.8% in this matchup; FG% +4.6% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 16.5 pts (3.0 pts below line; 57% blended confidence [T3]). Risk: L3 has surged to 27.7 after a 20-pt outing (9.4 above L30) — momentum could push over the under line.</t>
+          <t>Low scoring variance (σ=4.7) — highly predictable output near line — marginally supports the UNDER. Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Defense, H2H, Pace. Projection model targets 11.2 pts (1.3 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -13677,7 +13673,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13686,36 +13682,36 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.509</v>
+        <v>0.575</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>11.2</v>
+        <v>24.6</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
-        <v>1.637</v>
+        <v>1.746</v>
       </c>
       <c r="K97" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.7) — highly predictable output near line — marginally supports the UNDER. Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Defense, H2H, Pace. Projection model targets 11.2 pts (0.3 pts below line; 50% blended confidence [T3]).</t>
+          <t>Williamson averages 28.5 pts in 4 meetings (+7.0 vs line) — marginally supports the OVER. H2H avg 8.0 pts above season L30; TS% shifts +11.2% in this matchup. Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 3/10 agree (Defense, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 24.6 pts (3.1 pts above line; 57% blended confidence [T3]). Risk: only 40% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -13725,45 +13721,45 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.575</v>
+        <v>0.589</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>24.6</v>
+        <v>8</v>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J98" t="n">
-        <v>1.676</v>
+        <v>1.775</v>
       </c>
       <c r="K98" t="n">
-        <v>2.08</v>
+        <v>1.943</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>Williamson averages 28.5 pts in 4 meetings (+7.0 vs line) — marginally supports the OVER. H2H avg 8.0 pts above season L30; TS% shifts +11.2% in this matchup. Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 3/10 agree (Defense, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 24.6 pts (3.1 pts above line; 57% blended confidence [T3]). Risk: only 40% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Low scoring variance (σ=4.5) — highly predictable output near line — supports the UNDER. FG% -3.6% trending (L10 vs L30); Minutes down 2.6 recently (L10=19.6 vs L30=22.2). Opponent is weak defense (#29) at moderate pace (#15). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, H2H dissent. Projection model targets 8.0 pts (3.5 pts below line; 58% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -13778,40 +13774,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.627</v>
+        <v>0.584</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>8</v>
+        <v>16.3</v>
       </c>
       <c r="I99" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J99" t="n">
-        <v>2.15</v>
+        <v>1.971</v>
       </c>
       <c r="K99" t="n">
-        <v>1.629</v>
+        <v>1.746</v>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>Queen's L30 of 9.9 pts sits 2.6 below the 12.5 line — supports the UNDER. FG% -3.6% trending (L10 vs L30); Minutes down 2.6 recently (L10=19.6 vs L30=22.2). Opponent is weak defense (#29) at moderate pace (#15). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, H2H dissent. Projection model targets 8.0 pts (4.5 pts below line; 62% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 4/10 agree (HR L30, HR L10, Trend); counter-signals: Volume, Defense, H2H. Projection model targets 16.3 pts (3.2 pts below line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -13821,7 +13817,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13830,36 +13826,36 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.584</v>
+        <v>0.537</v>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
-        <v>1.893</v>
+        <v>1.599</v>
       </c>
       <c r="K100" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. Opponent is weak defense (#25) at moderate pace (#15). Mixed signals: 4/10 agree (HR L30, HR L10, Trend); counter-signals: Volume, Defense, H2H. Projection model targets 16.3 pts (3.2 pts below line; 58% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — marginally supports the OVER. FG% +6.4% trending (L10 vs L30); Minutes up 3.4 recently (L10=20.7 vs L30=17.3). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 15.0 pts (1.5 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=8.0) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -13869,7 +13865,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13878,36 +13874,36 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.571</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
-        <v>1.775</v>
+        <v>1.82</v>
       </c>
       <c r="K101" t="n">
-        <v>1.943</v>
+        <v>1.893</v>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — supports the OVER. FG% +6.4% trending (L10 vs L30); Minutes up 3.4 recently (L10=20.7 vs L30=17.3). Opponent is weak defense (#23) at above-average pace (#6). 6/10 signals agree — HR L10, Trend, Defense, Pace support the OVER; Volume, HR L30, Context dissent. Projection model targets 15.0 pts (2.5 pts above line; 57% blended confidence [T2]). Risk: high variance (σ=8.0) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=2.8) — highly predictable output near line — supports the UNDER. FG% -5.9% trending (L10 vs L30). Opponent is weak defense (#29) at moderate pace (#15). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, Min Trend dissent. Projection model targets 4.3 pts (2.2 pts below line; 55% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -13917,45 +13913,45 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="F102" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>4.3</v>
+        <v>18.3</v>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
-        <v>1.971</v>
+        <v>1.806</v>
       </c>
       <c r="K102" t="n">
-        <v>1.746</v>
+        <v>1.909</v>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=2.8) — highly predictable output near line — supports the UNDER. FG% -5.9% trending (L10 vs L30). Opponent is weak defense (#29) at moderate pace (#15). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, Min Trend dissent. Projection model targets 4.3 pts (2.2 pts below line; 55% blended confidence [T2]).</t>
+          <t>Recent scoring trending up 5.0 pts (L5 vs L30) — marginally supports the OVER. TS% shifts +10.3% in this matchup; FG% +5.6% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 18.3 pts (2.8 pts above line; 56% blended confidence [T3]). Risk: only 30% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -13965,7 +13961,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13974,7 +13970,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.597</v>
+        <v>0.528</v>
       </c>
       <c r="F103" t="n">
         <v>5</v>
@@ -13983,27 +13979,27 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>18.3</v>
+        <v>8.5</v>
       </c>
       <c r="I103" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>2.1</v>
+        <v>1.735</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 5.0 pts (L5 vs L30) — marginally supports the OVER. TS% shifts +10.3% in this matchup; FG% +5.6% trending (L10 vs L30). Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 18.3 pts (3.8 pts above line; 59% blended confidence [T3]). Risk: only 30% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Low scoring variance (σ=3.1) — highly predictable output near line — marginally supports the UNDER. TS% shifts -10.8% in this matchup. Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.5 pts (1.0 pts below line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -14013,7 +14009,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14022,36 +14018,36 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.528</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>8.5</v>
+        <v>16.4</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
-        <v>1.943</v>
+        <v>1.719</v>
       </c>
       <c r="K104" t="n">
-        <v>1.775</v>
+        <v>2.02</v>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=3.1) — highly predictable output near line — marginally supports the UNDER. TS% shifts -10.8% in this matchup. Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.5 pts (1.0 pts below line; 52% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 2.4 pts (L5 vs L30) — supports the OVER. Minutes up 2.5 recently (L10=32.7 vs L30=30.2). Opponent is weak defense (#25) at above-average pace (#6). 6/10 signals agree — Volume, HR L10, Context, Defense support the OVER; HR L30, Trend, H2H dissent. Projection model targets 16.4 pts (1.9 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -14061,7 +14057,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14070,36 +14066,36 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>16.4</v>
+        <v>19.1</v>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
-        <v>1.787</v>
+        <v>1.73</v>
       </c>
       <c r="K105" t="n">
-        <v>1.926</v>
+        <v>2.02</v>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.4 pts (L5 vs L30) — supports the OVER. Minutes up 2.5 recently (L10=32.7 vs L30=30.2). Opponent is weak defense (#25) at above-average pace (#6). 6/10 signals agree — Volume, HR L10, Context, Defense support the OVER; HR L30, Trend, H2H dissent. Projection model targets 16.4 pts (1.9 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 3.1 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 2.1 pts below season L30; TS% shifts -4.9% in this matchup. Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (HR L30, Trend, Context); counter-signals: Volume, HR L10, Defense. Projection model targets 19.1 pts (2.4 pts below line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -14109,16 +14105,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.511</v>
       </c>
       <c r="F106" t="n">
         <v>5</v>
@@ -14127,20 +14123,20 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>19.1</v>
+        <v>4.7</v>
       </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J106" t="n">
-        <v>1.847</v>
+        <v>2.9</v>
       </c>
       <c r="K106" t="n">
-        <v>1.926</v>
+        <v>1.385</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.1 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 2.1 pts below season L30; TS% shifts -4.9% in this matchup. Opponent is below-average defense (#16) at moderate pace (#15). Mixed signals: 5/10 agree (HR L30, Trend, Context); counter-signals: Volume, HR L10, Defense. Projection model targets 19.1 pts (2.4 pts below line; 56% blended confidence [T3]).</t>
+          <t>[Low conviction — lean only] Low scoring variance (σ=2.7) — highly predictable output near line — marginally supports the lean OVER. FG% -6.1% trending (L10 vs L30); Minutes down 3.9 recently (L10=17.0 vs L30=20.9). Opponent is weak defense (#25) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, H2H. Projection model targets 4.7 pts (0.2 pts above line; 51% blended confidence [T3_LEAN]). Risk: minutes trending down (17.0 L10 vs 20.9 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -14253,7 +14249,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Sheppard</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14263,17 +14259,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Ben Sheppard</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -14283,17 +14279,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Obi Toppin</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14303,17 +14299,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Obi Toppin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14323,17 +14319,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14343,17 +14339,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -14367,13 +14363,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14387,13 +14383,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jay Huff</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -14403,17 +14399,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Jay Huff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -14427,7 +14423,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="13">
@@ -14447,7 +14443,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="14">
@@ -14507,7 +14503,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="17">
@@ -14527,7 +14523,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
@@ -14687,7 +14683,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="26">
@@ -14827,7 +14823,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="33">
@@ -15007,7 +15003,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="42">
@@ -15027,7 +15023,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="43">
@@ -15207,7 +15203,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="52">
@@ -15267,7 +15263,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55">
@@ -15407,7 +15403,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="62">
@@ -15427,7 +15423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="63">
@@ -15507,7 +15503,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="67">
@@ -15603,11 +15599,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="72">
@@ -15703,11 +15699,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="77">
@@ -15883,11 +15879,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="86">
@@ -15907,7 +15903,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="87">
@@ -16007,7 +16003,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="92">
@@ -16053,7 +16049,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Malik Monk</t>
+          <t>Jeremiah Fears</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -16063,7 +16059,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -16073,7 +16069,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jeremiah Fears</t>
+          <t>DeMar DeRozan</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -16083,17 +16079,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>Nique Clifford</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -16107,13 +16103,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Nique Clifford</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -16123,17 +16119,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -16143,17 +16139,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -16167,13 +16163,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>Devin Carter</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -16183,17 +16179,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Devin Carter</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -16203,17 +16199,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Precious Achiuwa</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -16223,17 +16219,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Precious Achiuwa</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -16243,17 +16239,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Maxime Raynaud</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -16263,17 +16259,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Maxime Raynaud</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -16283,17 +16279,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>14.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Dylan Cardwell</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -16303,11 +16299,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>21.5</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-03.xlsx
+++ b/daily/2026-04-03.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1612,7 +1630,6 @@
       <c r="V14" t="n">
         <v>21</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>6.5</v>
       </c>
@@ -1690,7 +1707,6 @@
       <c r="V15" t="n">
         <v>16</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>-22.4</v>
       </c>
@@ -1842,7 +1858,7 @@
         <v>-1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>15</v>
@@ -1850,7 +1866,6 @@
       <c r="V17" t="n">
         <v>23</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>-0.6</v>
       </c>
@@ -1928,7 +1943,6 @@
       <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>7.4</v>
       </c>
@@ -2006,7 +2020,6 @@
       <c r="V19" t="n">
         <v>16</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>0</v>
       </c>
@@ -2084,7 +2097,6 @@
       <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>-18.7</v>
       </c>
@@ -2162,7 +2174,6 @@
       <c r="V21" t="n">
         <v>16</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>2.5</v>
       </c>
@@ -2240,7 +2251,6 @@
       <c r="V22" t="n">
         <v>23</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>22.7</v>
       </c>
@@ -2638,7 +2648,7 @@
         <v>7.3</v>
       </c>
       <c r="T27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>14</v>
@@ -2646,7 +2656,6 @@
       <c r="V27" t="n">
         <v>16</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>8.5</v>
       </c>
@@ -2888,7 +2897,6 @@
       <c r="V30" t="n">
         <v>7</v>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -3212,7 +3220,6 @@
       <c r="V34" t="n">
         <v>30</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-35.5</v>
       </c>
@@ -3290,7 +3297,6 @@
       <c r="V35" t="n">
         <v>7</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>-10.8</v>
       </c>
@@ -3368,7 +3374,6 @@
       <c r="V36" t="n">
         <v>7</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>4.6</v>
       </c>
@@ -3692,7 +3697,6 @@
       <c r="V40" t="n">
         <v>1</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-32.2</v>
       </c>
@@ -4590,7 +4594,6 @@
       <c r="V51" t="n">
         <v>24</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>19.6</v>
       </c>
@@ -5799,7 +5802,7 @@
         <v>33</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>4.1</v>
@@ -6226,7 +6229,6 @@
       <c r="V71" t="n">
         <v>5</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>17.3</v>
       </c>
@@ -6304,7 +6306,6 @@
       <c r="V72" t="n">
         <v>25</v>
       </c>
-      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>21.9</v>
       </c>
@@ -6382,7 +6383,6 @@
       <c r="V73" t="n">
         <v>25</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>0</v>
       </c>
@@ -6460,7 +6460,6 @@
       <c r="V74" t="n">
         <v>5</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>-4.6</v>
       </c>
@@ -6538,7 +6537,6 @@
       <c r="V75" t="n">
         <v>5</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>5.8</v>
       </c>
@@ -6616,7 +6614,6 @@
       <c r="V76" t="n">
         <v>5</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>25.5</v>
       </c>
@@ -6776,7 +6773,6 @@
       <c r="V78" t="n">
         <v>25</v>
       </c>
-      <c r="W78" t="inlineStr"/>
       <c r="X78" t="n">
         <v>2.7</v>
       </c>
@@ -6936,7 +6932,6 @@
       <c r="V80" t="n">
         <v>5</v>
       </c>
-      <c r="W80" t="inlineStr"/>
       <c r="X80" t="n">
         <v>0</v>
       </c>
@@ -7014,7 +7009,6 @@
       <c r="V81" t="n">
         <v>29</v>
       </c>
-      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>-1.7</v>
       </c>
@@ -7174,7 +7168,6 @@
       <c r="V83" t="n">
         <v>29</v>
       </c>
-      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
         <v>2</v>
       </c>
@@ -7416,7 +7409,6 @@
       <c r="V86" t="n">
         <v>2</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>-13.1</v>
       </c>
@@ -7576,7 +7568,6 @@
       <c r="V88" t="n">
         <v>2</v>
       </c>
-      <c r="W88" t="inlineStr"/>
       <c r="X88" t="n">
         <v>-7.8</v>
       </c>
@@ -7736,7 +7727,6 @@
       <c r="V90" t="n">
         <v>29</v>
       </c>
-      <c r="W90" t="inlineStr"/>
       <c r="X90" t="n">
         <v>-14.8</v>
       </c>
@@ -7978,7 +7968,6 @@
       <c r="V93" t="n">
         <v>2</v>
       </c>
-      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
         <v>2.2</v>
       </c>
@@ -8056,7 +8045,6 @@
       <c r="V94" t="n">
         <v>15</v>
       </c>
-      <c r="W94" t="inlineStr"/>
       <c r="X94" t="n">
         <v>6.2</v>
       </c>
@@ -8216,7 +8204,6 @@
       <c r="V96" t="n">
         <v>6</v>
       </c>
-      <c r="W96" t="inlineStr"/>
       <c r="X96" t="n">
         <v>-11.2</v>
       </c>
@@ -8376,7 +8363,6 @@
       <c r="V98" t="n">
         <v>15</v>
       </c>
-      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
         <v>-0.2</v>
       </c>
@@ -8446,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>25</v>
@@ -8454,7 +8440,6 @@
       <c r="V99" t="n">
         <v>15</v>
       </c>
-      <c r="W99" t="inlineStr"/>
       <c r="X99" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -8532,7 +8517,6 @@
       <c r="V100" t="n">
         <v>6</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="n">
         <v>4.5</v>
       </c>
@@ -8856,7 +8840,6 @@
       <c r="V104" t="n">
         <v>6</v>
       </c>
-      <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
         <v>3</v>
       </c>
@@ -9016,7 +8999,6 @@
       <c r="V106" t="n">
         <v>6</v>
       </c>
-      <c r="W106" t="inlineStr"/>
       <c r="X106" t="n">
         <v>1.7</v>
       </c>
@@ -14207,2103 +14189,4773 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jackson scored 16 pts vs 10.5 line (+5.5), UNDER missed by 5.5 pts. Jackson played 25 min (+9.1 vs L10 avg of 16.1) — 57% more than expected. Shooting efficiency was hot: 75.0% FG (+32.3% vs L10 avg of 42.7%). 6/8 from the field. All 10 agreeing signals (Volume, HR L30, HR L10, Trend) were wrong — result went directly against the consensus. Projection model targeted 7.8 pts — actual 16 was 8.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Siakam scored 30 pts vs 21.5 line (+8.5), OVER hit by 8.5 pts. Siakam played 34 min (+4.1 vs L10 avg of 29.8) — 14% more than expected. Shooting was in line with averages: 54.2% FG (13/24, L10 avg 49.4%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 22.3 pts — actual 30 was 7.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Siakam's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ball scored 18 pts vs 19.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 27.9. Shooting was in line with averages: 40.0% FG (6/15, L10 avg 43.4%). Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.3 pts — actual 18 was 4.3 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Ben Sheppard</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sheppard scored 7 pts vs 7.5 line (-0.5), OVER missed by 0.5 pts. Sheppard played 25 min (+5.6 vs L10 avg of 19.0) — 29% more than expected. Shooting efficiency was cold: 28.6% FG (-29.9% vs L10 avg of 58.5%). 2/7 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.7 pts — actual 7 was 0.7 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 20 pts vs 17.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 30 played vs L10 avg 28.5. Shooting efficiency was hot: 58.3% FG (+15.5% vs L10 avg of 42.8%). 7/12 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 22.5 pts — actual 20 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Knueppel's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Obi Toppin</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Toppin scored 11 pts vs 9.5 line (+1.5), UNDER missed by 1.5 pts. Toppin played 20 min (+3.1 vs L10 avg of 16.9) — 18% more than expected. Shooting efficiency was cold: 44.4% FG (-13.4% vs L10 avg of 57.8%). 4/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 5.0 pts — actual 11 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 22 pts vs 20.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 30.3. Shooting efficiency was hot: 52.9% FG (+7.0% vs L10 avg of 45.9%). 9/17 from the field. Signals that called it correctly: HR L30, Trend, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: Volume, HR L10, Min Trend. Projection model targeted 20.7 pts — actual 22 was 1.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Miller in this role.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 19 pts vs 14.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 26 played vs L10 avg 28.0. Shooting efficiency was cold: 43.8% FG (-10.5% vs L10 avg of 54.3%). 7/16 from the field. Counter-signals that proved correct: Volume, Trend, Defense, H2H. Signals that were wrong: HR L30, HR L10, Context. Projection model targeted 12.0 pts — actual 19 was 7.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Kobe Brown</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 12 pts vs 10.5 line (+1.5), UNDER missed by 1.5 pts. Brown played 28 min (+4.6 vs L10 avg of 23.4) — 20% more than expected. Shooting efficiency was cold: 50.0% FG (-5.3% vs L10 avg of 55.3%). 5/10 from the field. Counter-signals that proved correct: Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.8 pts — actual 12 was 7.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Huff scored 12 pts vs 9.5 line (+2.5), OVER hit by 2.5 pts. Huff played 24 min (+3.0 vs L10 avg of 21.0) — 14% more than expected. Shooting efficiency was cold: 27.8% FG (-24.5% vs L10 avg of 52.3%). 5/18 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 12.1 pts — actual 12 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Huff in this role.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — White scored 11 pts vs 15.5 line (-4.5), OVER missed by 4.5 pts. White played 14 min (-6.7 vs L10 avg of 20.9) — 32% less than expected. Shooting efficiency was cold: 42.9% FG (-6.1% vs L10 avg of 49.0%). 3/7 from the field. Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.5 pts — actual 11 was 7.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag White for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Kam Jones</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>IND @ CHA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 7 pts vs 7.5 line (-0.5), UNDER hit by 0.5 pts. Jones played 23 min (+3.7 vs L10 avg of 19.1) — 19% more than expected. Shooting efficiency was hot: 60.0% FG (+26.7% vs L10 avg of 33.3%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Min Trend. Projection model targeted 1.8 pts — actual 7 was 5.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 23 pts vs 15.5 line (+7.5), UNDER missed by 7.5 pts. George played 38 min (+5.4 vs L10 avg of 32.6) — 17% more than expected. Shooting efficiency was cold: 40.0% FG (-7.8% vs L10 avg of 47.8%). 6/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, Pace. Projection model targeted 9.3 pts — actual 23 was 13.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — DiVincenzo scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 29 played vs L10 avg 30.7. Shooting efficiency was cold: 27.3% FG (-8.4% vs L10 avg of 35.7%). 3/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.9 pts — actual 11 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for DiVincenzo in this role.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Reid scored 12 pts vs 12.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 29 played vs L10 avg 26.1. Shooting efficiency was cold: 35.7% FG (-5.1% vs L10 avg of 40.8%). 5/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context. Projection model targeted 14.6 pts — actual 12 was 2.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 21 pts vs 26.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 35 played vs L10 avg 37.2. Shooting efficiency was hot: 53.8% FG (+8.2% vs L10 avg of 45.6%). 7/13 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 37.5 pts — actual 21 was 16.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Embiid scored 19 pts vs 28.5 line (-9.5), OVER missed by 9.5 pts. Minutes were as expected: 34 played vs L10 avg 33.4. Shooting efficiency was cold: 35.3% FG (-17.2% vs L10 avg of 52.5%). 6/17 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 28.4 pts — actual 19 was 9.4 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 7 pts vs 5.5 line (+1.5), UNDER missed by 1.5 pts. Barlow played 26 min (+3.7 vs L10 avg of 22.1) — 17% more than expected. Shooting was in line with averages: 60.0% FG (3/5, L10 avg 59.9%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 2.8 pts — actual 7 was 4.2 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 21 pts vs 9.5 line (+11.5), OVER hit by 11.5 pts. Minutes were as expected: 30 played vs L10 avg 29.8. Shooting efficiency was hot: 66.7% FG (+21.4% vs L10 avg of 45.3%). 8/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 18.4 pts — actual 21 was 2.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gobert scored 5 pts vs 11.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 29 played vs L10 avg 31.1. Shooting efficiency was cold: 25.0% FG (-37.9% vs L10 avg of 62.9%). 2/8 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 19.2 pts — actual 5 was 14.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dosunmu scored 19 pts vs 15.5 line (+3.5), UNDER missed by 3.5 pts. Dosunmu played 36 min (+6.0 vs L10 avg of 30.2) — 20% more than expected. Shooting efficiency was cold: 37.5% FG (-15.9% vs L10 avg of 53.4%). 6/16 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, H2H. Projection model targeted 11.0 pts — actual 19 was 8.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Grimes scored 10 pts vs 8.5 line (+1.5), OVER hit by 1.5 pts. Grimes played 25 min (-6.6 vs L10 avg of 31.4) — 21% less than expected. Shooting efficiency was hot: 62.5% FG (+15.2% vs L10 avg of 47.3%). 5/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 17.6 pts — actual 10 was 7.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Grimes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Anthony Edwards</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Edwards scored 8 pts vs 24.5 line (-16.5), UNDER hit by 16.5 pts. Edwards played 26 min (-7.9 vs L10 avg of 34.1) — 23% less than expected. Shooting efficiency was cold: 20.0% FG (-28.6% vs L10 avg of 48.6%). 3/15 from the field. Signals that called it correctly: Trend, Pace, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.8 pts — actual 8 was 14.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Edwards's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Randle scored 21 pts vs 20.5 line (+0.5), UNDER missed by 0.5 pts. Randle played 37 min (+4.1 vs L10 avg of 32.7) — 13% more than expected. Shooting efficiency was hot: 60.0% FG (+12.5% vs L10 avg of 47.5%). 9/15 from the field. Counter-signals that proved correct: HR L10, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 13.5 pts — actual 21 was 7.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIN @ PHI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 8 pts vs 13.5 line (-5.5), OVER missed by 5.5 pts. Edgecombe played 37 min (+3.5 vs L10 avg of 33.3) — 11% more than expected. Shooting efficiency was cold: 44.4% FG (-7.8% vs L10 avg of 52.2%). 4/9 from the field. Counter-signals that proved correct: Defense, H2H, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 24.2 pts — actual 8 was 16.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Okongwu scored 15 pts vs 14.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 27 played vs L10 avg 29.2. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 45.3%). Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 14.0 pts — actual 15 was 1.0 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — McCollum scored 25 pts vs 17.5 line (+7.5), UNDER missed by 7.5 pts. McCollum played 25 min (-4.5 vs L10 avg of 29.9) — 15% less than expected. Shooting efficiency was hot: 66.7% FG (+20.3% vs L10 avg of 46.4%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, Pace. Projection model targeted 15.4 pts — actual 25 was 9.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag McCollum for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Traore scored 13 pts vs 11.5 line (+1.5), UNDER missed by 1.5 pts. Traore played 30 min (+7.5 vs L10 avg of 22.0) — 34% more than expected. Shooting efficiency was hot: 45.5% FG (+17.5% vs L10 avg of 28.0%). 5/11 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.1 pts — actual 13 was 1.9 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Alexander-Walker scored 21 pts vs 19.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 34 played vs L10 avg 33.0. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 53.4%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 21.0 pts — actual 21 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Alexander-Walker in this role.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clowney scored 12 pts vs 10.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 21 played vs L10 avg 21.4. Shooting efficiency was hot: 57.1% FG (+23.6% vs L10 avg of 33.5%). 4/7 from the field. Counter-signals that proved correct: Volume, Defense, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 7.7 pts — actual 12 was 4.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 18 pts vs 22.5 line (-4.5), UNDER hit by 4.5 pts. Johnson played 28 min (-8.7 vs L10 avg of 36.2) — 24% less than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 48.2%). Signals that called it correctly: Volume, Context, H2H, Pace (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 20.5 pts — actual 18 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Johnson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kuminga scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 20.3. Shooting efficiency was hot: 66.7% FG (+28.1% vs L10 avg of 38.6%). 4/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, H2H. Projection model targeted 1.3 pts — actual 12 was 10.7 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Powell scored 6 pts vs 8.5 line (-2.5), UNDER hit by 2.5 pts. Powell played 29 min (+3.1 vs L10 avg of 25.5) — 12% more than expected. Shooting efficiency was cold: 28.6% FG (-11.9% vs L10 avg of 40.5%). 2/7 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.1 pts — actual 6 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Powell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Ziaire Williams</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 8 pts vs 10.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 21 played vs L10 avg 22.4. Shooting efficiency was cold: 20.0% FG (-27.9% vs L10 avg of 47.9%). 2/10 from the field. Counter-signals that proved correct: H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.4 pts — actual 8 was 2.4 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Daniels scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 30 played vs L10 avg 32.2. Shooting efficiency was hot: 62.5% FG (+7.3% vs L10 avg of 55.2%). 5/8 from the field. Signals that called it correctly: Context, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.0 pts — actual 11 was 2.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Daniels in this role.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>ATL @ BKN</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Risacher scored 2 pts vs 7.5 line (-5.5), OVER missed by 5.5 pts. Risacher played 12 min (-4.0 vs L10 avg of 16.5) — 24% less than expected. Shooting efficiency was cold: 33.3% FG (-29.1% vs L10 avg of 62.4%). 1/3 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Pace. Signals that were wrong: Volume, Context, Defense. Projection model targeted 10.3 pts — actual 2 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Buzelis scored 11 pts vs 17.5 line (-6.5), UNDER hit by 6.5 pts. Buzelis played 23 min (-9.3 vs L10 avg of 32.5) — 29% less than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 43.7%). Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.6 pts — actual 11 was 3.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Buzelis's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Mitchell Robinson</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Robinson scored 17 pts vs 6.5 line (+10.5), UNDER missed by 10.5 pts. Minutes were as expected: 23 played vs L10 avg 21.1. Shooting efficiency was hot: 100.0% FG (+25.2% vs L10 avg of 74.8%). 7/7 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 2.4 pts — actual 17 was 14.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Okoro scored 7 pts vs 8.5 line (-1.5), OVER missed by 1.5 pts. Okoro played 26 min (-3.3 vs L10 avg of 29.7) — 11% less than expected. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 45.1%). Counter-signals that proved correct: HR L10, Defense, Pace. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 10.7 pts — actual 7 was 3.7 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hart scored 7 pts vs 12.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 28 played vs L10 avg 30.9. Shooting was in line with averages: 60.0% FG (3/5, L10 avg 56.8%). Signals that called it correctly: Volume, HR L30, Trend, Context, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Defense, Pace. Projection model targeted 5.7 pts — actual 7 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hart in this role.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 13 pts vs 13.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 27.6. Shooting efficiency was hot: 80.0% FG (+21.1% vs L10 avg of 58.9%). 4/5 from the field. Signals that called it correctly: Defense, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.9 pts — actual 13 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jones in this role.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Anunoby scored 31 pts vs 17.5 line (+13.5), UNDER missed by 13.5 pts. Anunoby played 30 min (-4.1 vs L10 avg of 34.6) — 12% less than expected. Shooting efficiency was hot: 60.0% FG (+12.0% vs L10 avg of 48.0%). 9/15 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, Pace. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 16.0 pts — actual 31 was 15.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Anunoby for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 12 pts vs 14.5 line (-2.5), UNDER hit by 2.5 pts. Bridges played 23 min (-9.6 vs L10 avg of 32.3) — 30% less than expected. Shooting efficiency was cold: 33.3% FG (-15.3% vs L10 avg of 48.6%). 4/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 12.3 pts — actual 12 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Bridges in this role.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Nick Richards</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="5" t="n">
         <v>8.5</v>
       </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Josh Giddey</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Giddey scored 6 pts vs 15.5 line (-9.5), OVER missed by 9.5 pts. Giddey played 26 min (-9.3 vs L10 avg of 35.0) — 27% less than expected. Shooting efficiency was cold: 25.0% FG (-18.0% vs L10 avg of 43.0%). 3/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H, FG Trend. Projection model targeted 16.3 pts — actual 6 was 10.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Giddey for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>CHI @ NYK</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brunson scored 17 pts vs 26.5 line (-9.5), UNDER hit by 9.5 pts. Brunson played 30 min (-6.7 vs L10 avg of 36.6) — 18% less than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 46.5%). Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 24.4 pts — actual 17 was 7.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Brunson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Ryan Rollins</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="5" t="n">
         <v>18.5</v>
       </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dieng scored 9 pts vs 12.5 line (-3.5), UNDER hit by 3.5 pts. Dieng played 24 min (-5.3 vs L10 avg of 29.3) — 18% less than expected. Shooting efficiency was cold: 26.7% FG (-14.8% vs L10 avg of 41.5%). 4/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 11.4 pts — actual 9 was 2.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dieng's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Hauser scored 13 pts vs 8.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 27 played vs L10 avg 25.1. Shooting efficiency was hot: 83.3% FG (+44.3% vs L10 avg of 39.0%). 5/6 from the field. Counter-signals that proved correct: Volume, HR L30, Trend, Defense. Signals that were wrong: HR L10, Context, H2H. Projection model targeted 6.5 pts — actual 13 was 6.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Pritchard scored 16 pts vs 16.5 line (-0.5), OVER missed by 0.5 pts. Pritchard played 26 min (-5.3 vs L10 avg of 31.8) — 17% less than expected. Shooting efficiency was hot: 58.3% FG (+13.8% vs L10 avg of 44.5%). 7/12 from the field. Counter-signals that proved correct: HR L10, H2H, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 16.4 pts — actual 16 was 0.4 pts close (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Pritchard for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Gary Trent Jr.</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="5" t="n">
         <v>10.5</v>
       </c>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Myles Turner</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Turner scored 4 pts vs 10.5 line (-6.5), UNDER hit by 6.5 pts. Turner played 19 min (-5.7 vs L10 avg of 24.5) — 23% less than expected. Shooting efficiency was cold: 25.0% FG (-15.7% vs L10 avg of 40.7%). 1/4 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (9/10 aligned). Counter-signals that were wrong: Volume. Projection model targeted 5.0 pts — actual 4 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Brown scored 26 pts vs 25.5 line (+0.5), OVER hit by 0.5 pts. Brown played 30 min (-4.8 vs L10 avg of 35.0) — 14% less than expected. Shooting efficiency was cold: 41.2% FG (-5.0% vs L10 avg of 46.2%). 7/17 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 27.1 pts — actual 26 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Queta scored 19 pts vs 9.5 line (+9.5), UNDER missed by 9.5 pts. Minutes were as expected: 29 played vs L10 avg 28.3. Shooting efficiency was hot: 72.7% FG (+6.6% vs L10 avg of 66.1%). 8/11 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Pace. Signals that were wrong: HR L30, Context, Defense. Projection model targeted 7.0 pts — actual 19 was 12.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Kyle Kuzma</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kuzma scored 14 pts vs 12.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 25 played vs L10 avg 25.2. Shooting efficiency was cold: 42.9% FG (-8.2% vs L10 avg of 51.1%). 6/14 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 17.3 pts — actual 14 was 3.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Kuzma's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Tatum scored 23 pts vs 22.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 31 played vs L10 avg 32.4. Shooting efficiency was hot: 50.0% FG (+9.8% vs L10 avg of 40.2%). 8/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 22.5 pts — actual 23 was 0.5 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Tatum in this role.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIL</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E60" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — White scored 17 pts vs 15.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 34.4. Shooting efficiency was hot: 54.5% FG (+13.7% vs L10 avg of 40.8%). 6/11 from the field. Counter-signals that proved correct: Volume, Defense, Pace, FG Trend. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 11.9 pts — actual 17 was 5.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E61" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 21 pts vs 18.5 line (+2.5), UNDER missed by 2.5 pts. Thompson played 32 min (-7.3 vs L10 avg of 39.2) — 19% less than expected. Shooting efficiency was hot: 63.6% FG (+8.7% vs L10 avg of 54.9%). 7/11 from the field. Counter-signals that proved correct: Defense, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.9 pts — actual 21 was 4.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Thompson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Filipowski scored 17 pts vs 15.5 line (+1.5), UNDER missed by 1.5 pts. Filipowski played 30 min (+4.5 vs L10 avg of 25.8) — 17% more than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 50.2%). Counter-signals that proved correct: HR L10, Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.5 pts — actual 17 was 3.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 27 pts vs 14.5 line (+12.5), UNDER missed by 12.5 pts. Williams played 38 min (+5.1 vs L10 avg of 33.2) — 15% more than expected. Shooting efficiency was hot: 62.5% FG (+17.9% vs L10 avg of 44.6%). 10/16 from the field. Counter-signals that proved correct: HR L10, Trend, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.0 pts — actual 27 was 16.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bailey scored 22 pts vs 18.5 line (+3.5), UNDER missed by 3.5 pts. Bailey played 33 min (+3.3 vs L10 avg of 29.3) — 11% more than expected. Shooting was in line with averages: 52.9% FG (9/17, L10 avg 48.5%). Counter-signals that proved correct: FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.8 pts — actual 22 was 7.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 18 pts vs 15.5 line (+2.5), OVER hit by 2.5 pts. Jr. played 24 min (-13.7 vs L10 avg of 37.7) — 36% less than expected. Shooting was in line with averages: 37.5% FG (6/16, L10 avg 42.1%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, FG Trend. Projection model targeted 15.9 pts — actual 18 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E66" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sengun scored 19 pts vs 19.5 line (-0.5), OVER missed by 0.5 pts. Sengun played 28 min (-5.4 vs L10 avg of 33.0) — 16% less than expected. Shooting was in line with averages: 66.7% FG (8/12, L10 avg 64.8%). Counter-signals that proved correct: Volume, HR L30, HR L10. Signals that were wrong: Trend, Context, Defense. Projection model targeted 23.5 pts — actual 19 was 4.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Sengun for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Eason scored 16 pts vs 10.5 line (+5.5), UNDER missed by 5.5 pts. Eason played 22 min (-3.2 vs L10 avg of 25.1) — 13% less than expected. Shooting efficiency was hot: 70.0% FG (+38.9% vs L10 avg of 31.1%). 7/10 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.3 pts — actual 16 was 5.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sheppard scored 12 pts vs 15.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 29 played vs L10 avg 29.8. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 44.8%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 14.8 pts — actual 12 was 2.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sheppard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Durant scored 25 pts vs 23.5 line (+1.5), UNDER missed by 1.5 pts. Durant played 30 min (-5.8 vs L10 avg of 36.2) — 16% less than expected. Shooting efficiency was hot: 66.7% FG (+13.4% vs L10 avg of 53.3%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend. Projection model targeted 22.5 pts — actual 25 was 2.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Durant for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>UTA @ HOU</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sensabaugh scored 20 pts vs 20.5 line (-0.5), UNDER hit by 0.5 pts. Sensabaugh played 33 min (+3.7 vs L10 avg of 29.7) — 12% more than expected. Shooting efficiency was cold: 43.8% FG (-9.5% vs L10 avg of 53.3%). 7/16 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 19.5 pts — actual 20 was 0.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Sensabaugh in this role.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Ingram scored 17 pts vs 21.5 line (-4.5), UNDER hit by 4.5 pts. Ingram played 26 min (-8.0 vs L10 avg of 34.1) — 23% less than expected. Shooting efficiency was hot: 54.5% FG (+6.1% vs L10 avg of 48.4%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (5/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 20.5 pts — actual 17 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ingram's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 30 pts vs 15.5 line (+14.5), OVER hit by 14.5 pts. Jackson played 30 min (+4.2 vs L10 avg of 25.9) — 16% more than expected. Shooting efficiency was hot: 62.5% FG (+11.1% vs L10 avg of 51.4%). 10/16 from the field. Signals that called it correctly: Volume, HR L10, Context, Min Trend (4/10 aligned). Counter-signals that were wrong: HR L30, Trend, Defense. Projection model targeted 20.0 pts — actual 30 was 10.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jackson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Taylor Hendricks</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hendricks scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 25.4. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 41.4%). Signals that called it correctly: Volume, HR L30, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: HR L10, H2H, Min Trend. Projection model targeted 7.1 pts — actual 9 was 1.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hendricks in this role.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Walter scored 7 pts vs 10.5 line (-3.5), UNDER hit by 3.5 pts. Walter played 28 min (+3.2 vs L10 avg of 24.6) — 13% more than expected. Shooting efficiency was cold: 22.2% FG (-35.4% vs L10 avg of 57.6%). 2/9 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.4 pts — actual 7 was 0.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Walter in this role.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barrett scored 25 pts vs 21.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 29 played vs L10 avg 30.5. Shooting was in line with averages: 52.9% FG (9/17, L10 avg 53.1%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 24.1 pts — actual 25 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Barrett in this role.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Shead scored 11 pts vs 7.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 23 played vs L10 avg 25.9. Shooting efficiency was hot: 66.7% FG (+36.6% vs L10 avg of 30.1%). 2/3 from the field. Signals that called it correctly: Trend, Defense, Pace, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.5 pts — actual 11 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Shead's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 10 pts vs 18.5 line (-8.5), UNDER hit by 8.5 pts. Barnes played 23 min (-8.0 vs L10 avg of 31.3) — 26% less than expected. Shooting efficiency was hot: 66.7% FG (+12.1% vs L10 avg of 54.6%). 4/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 15.9 pts — actual 10 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barnes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Coward scored 15 pts vs 14.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 27 played vs L10 avg 24.9. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 43.3%). Counter-signals that proved correct: HR L10, Trend, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.2 pts — actual 15 was 3.8 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mamukelashvili scored 10 pts vs 11.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 21 played vs L10 avg 21.4. Shooting efficiency was cold: 40.0% FG (-20.2% vs L10 avg of 60.2%). 2/5 from the field. Signals that called it correctly: HR L30, Context, H2H, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 8.3 pts — actual 10 was 1.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mamukelashvili in this role.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>TOR @ MEM</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Poeltl scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Poeltl played 23 min (-3.0 vs L10 avg of 25.8) — 12% less than expected. Shooting was in line with averages: 66.7% FG (4/6, L10 avg 62.7%). Signals that called it correctly: Volume, HR L30, Context, FG Trend (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.4 pts — actual 8 was 1.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Poeltl in this role.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Brandon Williams</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 23 pts vs 13.5 line (+9.5), UNDER missed by 9.5 pts. Williams played 26 min (+4.8 vs L10 avg of 20.8) — 23% more than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 44.7%). Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 9.5 pts — actual 23 was 13.5 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DAL is involved.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 28 pts vs 11.5 line (+16.5), OVER hit by 16.5 pts. Jr. played 36 min (+6.6 vs L10 avg of 29.3) — 23% more than expected. Shooting efficiency was cold: 50.0% FG (-5.0% vs L10 avg of 55.0%). 8/16 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, H2H. Projection model targeted 11.5 pts — actual 28 was 16.5 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Daniel Gafford</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E83" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gafford scored 7 pts vs 11.5 line (-4.5), OVER missed by 4.5 pts. Gafford played 20 min (-3.7 vs L10 avg of 23.6) — 16% less than expected. Shooting efficiency was cold: 66.7% FG (-6.3% vs L10 avg of 73.0%). 2/3 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 14.8 pts — actual 7 was 7.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E84" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 27 pts vs 20.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 33 played vs L10 avg 32.7. Shooting efficiency was hot: 61.5% FG (+16.9% vs L10 avg of 44.6%). 8/13 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 21.1 pts — actual 27 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Klay Thompson</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 18 pts vs 9.5 line (+8.5), OVER hit by 8.5 pts. Minutes were as expected: 22 played vs L10 avg 21.1. Shooting efficiency was hot: 53.8% FG (+13.8% vs L10 avg of 40.0%). 7/13 from the field. Signals that called it correctly: Volume, Context, Defense, H2H (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 10.7 pts — actual 18 was 7.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Thompson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E86" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 18 pts vs 15.5 line (+2.5), UNDER missed by 2.5 pts. Wagner played 17 min (-8.5 vs L10 avg of 25.6) — 33% less than expected. Shooting efficiency was hot: 66.7% FG (+19.3% vs L10 avg of 47.4%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 11.6 pts — actual 18 was 6.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Wagner for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Naji Marshall</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E87" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Marshall scored 9 pts vs 16.5 line (-7.5), UNDER hit by 7.5 pts. Marshall played 24 min (-7.1 vs L10 avg of 30.8) — 23% less than expected. Shooting efficiency was cold: 25.0% FG (-21.5% vs L10 avg of 46.5%). 3/12 from the field. Signals that called it correctly: Defense, H2H, Pace, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.9 pts — actual 9 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Marshall's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E88" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Suggs scored 19 pts vs 14.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 31 played vs L10 avg 30.9. Shooting efficiency was hot: 66.7% FG (+24.3% vs L10 avg of 42.4%). 8/12 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.8 pts — actual 19 was 8.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Khris Middleton</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Middleton scored 0 pts vs 9.5 line (-9.5), OVER missed by 9.5 pts. Middleton played 12 min (-7.0 vs L10 avg of 19.2) — 36% less than expected. Shooting efficiency was cold: 0.0% FG (-35.4% vs L10 avg of 35.4%). 0/4 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, H2H. Projection model targeted 10.0 pts — actual 0 was 10.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Middleton for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Flagg scored 51 pts vs 23.5 line (+27.5), UNDER missed by 27.5 pts. Minutes were as expected: 34 played vs L10 avg 34.4. Shooting efficiency was hot: 63.3% FG (+16.9% vs L10 avg of 46.4%). 19/30 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 19.9 pts — actual 51 was 31.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Max Christie</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Christie scored 14 pts vs 9.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 28 played vs L10 avg 28.6. Shooting efficiency was hot: 57.1% FG (+12.8% vs L10 avg of 44.3%). 4/7 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, H2H. Projection model targeted 6.7 pts — actual 14 was 7.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 19 pts vs 8.5 line (+10.5), OVER hit by 10.5 pts. Minutes were as expected: 29 played vs L10 avg 27.8. Shooting efficiency was hot: 54.5% FG (+11.0% vs L10 avg of 43.5%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: FG Trend, Min Trend. Projection model targeted 10.6 pts — actual 19 was 8.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>ORL @ DAL</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>23.5</v>
       </c>
+      <c r="E93" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Banchero scored 10 pts vs 23.5 line (-13.5), UNDER hit by 13.5 pts. Banchero played 31 min (-3.0 vs L10 avg of 34.1) — 9% less than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 39.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 22.1 pts — actual 10 was 12.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Banchero's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Jeremiah Fears</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Fears scored 28 pts vs 14.5 line (+13.5), UNDER missed by 13.5 pts. Fears played 37 min (+14.9 vs L10 avg of 22.1) — 67% more than expected. Shooting efficiency was hot: 52.6% FG (+6.0% vs L10 avg of 46.6%). 10/19 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.5 pts — actual 28 was 13.5 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>DeMar DeRozan</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>WIN — DeRozan scored 14 pts vs 20.5 line (-6.5), UNDER hit by 6.5 pts. DeRozan played 24 min (-8.5 vs L10 avg of 32.0) — 27% less than expected. Shooting efficiency was hot: 63.6% FG (+13.1% vs L10 avg of 50.5%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 16.5 pts — actual 14 was 2.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms DeRozan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E96" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clifford scored 23 pts vs 12.5 line (+10.5), UNDER missed by 10.5 pts. Clifford played 39 min (+5.8 vs L10 avg of 32.8) — 18% more than expected. Shooting efficiency was hot: 56.2% FG (+14.6% vs L10 avg of 41.6%). 9/16 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.2 pts — actual 23 was 11.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E97" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williamson scored 13 pts vs 21.5 line (-8.5), OVER missed by 8.5 pts. Minutes were as expected: 28 played vs L10 avg 30.6. Shooting efficiency was cold: 45.5% FG (-26.0% vs L10 avg of 71.5%). 5/11 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, FG Trend. Projection model targeted 24.6 pts — actual 13 was 11.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Queen scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Queen played 28 min (+8.0 vs L10 avg of 19.6) — 41% more than expected. Shooting efficiency was cold: 30.0% FG (-9.1% vs L10 avg of 39.1%). 3/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 8.0 pts — actual 8 was 0.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Queen in this role.</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E99" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bey scored 20 pts vs 19.5 line (+0.5), UNDER missed by 0.5 pts. Bey played 29 min (-3.5 vs L10 avg of 32.7) — 11% less than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 44.7%). Counter-signals that proved correct: Volume, Defense, H2H, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 16.3 pts — actual 20 was 3.7 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E100" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Carter scored 9 pts vs 13.5 line (-4.5), OVER missed by 4.5 pts. Carter played 32 min (+11.0 vs L10 avg of 20.7) — 53% more than expected. Shooting efficiency was cold: 30.0% FG (-8.6% vs L10 avg of 38.6%). 3/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 15.0 pts — actual 9 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Yves Missi</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Missi scored 6 pts vs 6.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 22.6. Shooting efficiency was cold: 40.0% FG (-8.6% vs L10 avg of 48.6%). 2/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 4.3 pts — actual 6 was 1.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Missi in this role.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E102" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Achiuwa scored 12 pts vs 15.5 line (-3.5), OVER missed by 3.5 pts. Achiuwa played 25 min (-6.9 vs L10 avg of 31.8) — 22% less than expected. Shooting was in line with averages: 60.0% FG (6/10, L10 avg 57.6%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 18.3 pts — actual 12 was 6.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Achiuwa for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E103" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 3 pts vs 9.5 line (-6.5), UNDER hit by 6.5 pts. Jones played 13 min (-17.0 vs L10 avg of 29.8) — 57% less than expected. Shooting was in line with averages: 33.3% FG (1/3, L10 avg 37.2%). Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.5 pts — actual 3 was 5.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Raynaud scored 28 pts vs 14.5 line (+13.5), OVER hit by 13.5 pts. Raynaud played 29 min (-3.7 vs L10 avg of 32.7) — 11% less than expected. Shooting efficiency was hot: 78.6% FG (+21.1% vs L10 avg of 57.5%). 11/14 from the field. Signals that called it correctly: Volume, HR L10, Context, Defense, Pace (6/10 aligned). Counter-signals that were wrong: HR L30, Trend, H2H. Projection model targeted 16.4 pts — actual 28 was 11.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Raynaud's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E105" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>WIN — III scored 13 pts vs 21.5 line (-8.5), UNDER hit by 8.5 pts. III played 32 min (-4.4 vs L10 avg of 36.2) — 12% less than expected. Shooting efficiency was hot: 55.6% FG (+11.9% vs L10 avg of 43.7%). 5/9 from the field. Signals that called it correctly: HR L30, Trend, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Defense. Projection model targeted 19.1 pts — actual 13 was 6.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms III's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Dylan Cardwell</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>NOP @ SAC</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="4" t="n">
         <v>4.5</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Cardwell scored 6 pts vs 4.5 line (+1.5), OVER hit by 1.5 pts. Cardwell played 24 min (+6.6 vs L10 avg of 17.0) — 39% more than expected. Shooting efficiency was hot: 100.0% FG (+48.7% vs L10 avg of 51.3%). 3/3 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 4.7 pts — actual 6 was 1.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Cardwell in this role.</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-04 12:51</t>
+        </is>
       </c>
     </row>
   </sheetData>
